--- a/content/blog/Backlog_Blog_Continental_Media.xlsx
+++ b/content/blog/Backlog_Blog_Continental_Media.xlsx
@@ -1564,7 +1564,7 @@
       <c r="V2" s="40" t="n"/>
       <c r="W2" s="40" t="inlineStr">
         <is>
-          <t>Idea</t>
+          <t>Publicado</t>
         </is>
       </c>
       <c r="X2" s="41" t="n">

--- a/content/blog/Backlog_Blog_Continental_Media.xlsx
+++ b/content/blog/Backlog_Blog_Continental_Media.xlsx
@@ -25,8 +25,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -156,7 +157,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -302,6 +303,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -654,7 +656,7 @@
         </is>
       </c>
       <c r="F4" s="33">
-        <f>MIN(Backlog!X2:X101)</f>
+        <f>MIN(Backlog!X2:X103)</f>
         <v/>
       </c>
     </row>
@@ -665,7 +667,7 @@
         </is>
       </c>
       <c r="B5" s="32">
-        <f>COUNTA(Backlog!A2:A101)</f>
+        <f>COUNTA(Backlog!A2:A103)</f>
         <v/>
       </c>
       <c r="C5" s="32" t="inlineStr">
@@ -679,7 +681,7 @@
         </is>
       </c>
       <c r="F5" s="34">
-        <f>COUNTIF(Backlog!X2:X101,F4)</f>
+        <f>COUNTIF(Backlog!X2:X103,F4)</f>
         <v/>
       </c>
     </row>
@@ -690,7 +692,7 @@
         </is>
       </c>
       <c r="B6" s="32">
-        <f>COUNTIF(Backlog!B2:B101,"Editorial")</f>
+        <f>COUNTIF(Backlog!B2:B103,"Editorial")</f>
         <v/>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -704,7 +706,7 @@
         </is>
       </c>
       <c r="F6" s="33">
-        <f>MIN(Backlog!X2:X101)+1</f>
+        <f>MIN(Backlog!X2:X103)+1</f>
         <v/>
       </c>
     </row>
@@ -715,7 +717,7 @@
         </is>
       </c>
       <c r="B7" s="32">
-        <f>COUNTIF(Backlog!B2:B101,"Guía práctica")</f>
+        <f>COUNTIF(Backlog!B2:B103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="C7" s="32" t="inlineStr">
@@ -729,7 +731,7 @@
         </is>
       </c>
       <c r="F7" s="33">
-        <f>MAX(Backlog!X2:X101)</f>
+        <f>MAX(Backlog!X2:X103)</f>
         <v/>
       </c>
     </row>
@@ -740,7 +742,7 @@
         </is>
       </c>
       <c r="B8" s="32">
-        <f>COUNTIFS(Backlog!B2:B101,"Guía práctica",Backlog!O2:O101,"?*",Backlog!O2:O101,"&lt;&gt;—")</f>
+        <f>COUNTIFS(Backlog!B2:B103,"Guía práctica",Backlog!O2:O103,"?*",Backlog!O2:O103,"&lt;&gt;—")</f>
         <v/>
       </c>
       <c r="C8" s="32" t="inlineStr">
@@ -754,7 +756,7 @@
         </is>
       </c>
       <c r="F8" s="34">
-        <f>MAX(Backlog!Z2:Z101)</f>
+        <f>MAX(Backlog!Z2:Z103)</f>
         <v/>
       </c>
     </row>
@@ -765,7 +767,7 @@
         </is>
       </c>
       <c r="B9" s="32">
-        <f>COUNTIF(Backlog!K2:K101,"Re-redacción 2026")</f>
+        <f>COUNTIF(Backlog!K2:K103,"Re-redacción 2026")</f>
         <v/>
       </c>
       <c r="C9" s="32" t="inlineStr">
@@ -779,7 +781,7 @@
         </is>
       </c>
       <c r="F9" s="34">
-        <f>COUNTIFS(Backlog!AA2:AA101,"Calendario semanal",Backlog!Y2:Y101,"&lt;&gt;martes",Backlog!Y2:Y101,"&lt;&gt;jueves")</f>
+        <f>COUNTIFS(Backlog!AA2:AA103,"Calendario semanal",Backlog!Y2:Y103,"&lt;&gt;martes",Backlog!Y2:Y103,"&lt;&gt;jueves")</f>
         <v/>
       </c>
     </row>
@@ -790,7 +792,7 @@
         </is>
       </c>
       <c r="B10" s="32">
-        <f>COUNTIF(Backlog!K2:K101,"Nuevo")</f>
+        <f>COUNTIF(Backlog!K2:K103,"Nuevo")</f>
         <v/>
       </c>
       <c r="C10" s="32" t="n"/>
@@ -802,7 +804,7 @@
         </is>
       </c>
       <c r="B11" s="32">
-        <f>COUNTIF(Backlog!R2:R101,"Alta")</f>
+        <f>COUNTIF(Backlog!R2:R103,"Alta")</f>
         <v/>
       </c>
       <c r="C11" s="32" t="n"/>
@@ -814,7 +816,7 @@
         </is>
       </c>
       <c r="B12" s="32">
-        <f>COUNTIF(Backlog!R2:R101,"Media")</f>
+        <f>COUNTIF(Backlog!R2:R103,"Media")</f>
         <v/>
       </c>
       <c r="C12" s="32" t="n"/>
@@ -826,7 +828,7 @@
         </is>
       </c>
       <c r="B13" s="32">
-        <f>COUNTIF(Backlog!R2:R101,"Baja")</f>
+        <f>COUNTIF(Backlog!R2:R103,"Baja")</f>
         <v/>
       </c>
       <c r="C13" s="32" t="n"/>
@@ -1024,11 +1026,11 @@
         </is>
       </c>
       <c r="B28" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A28,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A28,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C28" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A28,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A28,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1039,11 +1041,11 @@
         </is>
       </c>
       <c r="B29" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A29,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A29,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C29" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A29,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A29,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1054,11 +1056,11 @@
         </is>
       </c>
       <c r="B30" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A30,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A30,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C30" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A30,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A30,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1069,11 +1071,11 @@
         </is>
       </c>
       <c r="B31" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A31,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A31,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C31" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A31,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A31,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1084,11 +1086,11 @@
         </is>
       </c>
       <c r="B32" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A32,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A32,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C32" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A32,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A32,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1099,11 +1101,11 @@
         </is>
       </c>
       <c r="B33" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A33,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A33,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C33" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A33,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A33,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1114,11 +1116,11 @@
         </is>
       </c>
       <c r="B34" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A34,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A34,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C34" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A34,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A34,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1129,11 +1131,11 @@
         </is>
       </c>
       <c r="B35" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A35,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A35,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C35" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A35,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A35,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1144,11 +1146,11 @@
         </is>
       </c>
       <c r="B36" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A36,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A36,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C36" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A36,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A36,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1159,11 +1161,11 @@
         </is>
       </c>
       <c r="B37" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A37,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A37,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C37" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A37,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A37,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1174,11 +1176,11 @@
         </is>
       </c>
       <c r="B38" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A38,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A38,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C38" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A38,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A38,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1189,11 +1191,11 @@
         </is>
       </c>
       <c r="B39" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A39,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A39,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="C39" s="32">
-        <f>COUNTIFS(Backlog!$T$2:$T$101,A39,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$T$2:$T$103,A39,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
     </row>
@@ -1300,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AA101"/>
+  <dimension ref="A1:AA103"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="7" customWidth="1" style="27" min="1" max="1"/>
@@ -1575,11 +1577,11 @@
         <v/>
       </c>
       <c r="Z2" s="42">
-        <f>INT((X2-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X2-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA2" s="42">
-        <f>IF(X2=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X2=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -1688,11 +1690,11 @@
         <v/>
       </c>
       <c r="Z3" s="42">
-        <f>INT((X3-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X3-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA3" s="42">
-        <f>IF(X3=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X3=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -1801,11 +1803,11 @@
         <v/>
       </c>
       <c r="Z4" s="42">
-        <f>INT((X4-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X4-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA4" s="42">
-        <f>IF(X4=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X4=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -1918,11 +1920,11 @@
         <v/>
       </c>
       <c r="Z5" s="42">
-        <f>INT((X5-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X5-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA5" s="42">
-        <f>IF(X5=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X5=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2031,11 +2033,11 @@
         <v/>
       </c>
       <c r="Z6" s="42">
-        <f>INT((X6-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X6-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA6" s="42">
-        <f>IF(X6=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X6=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2144,11 +2146,11 @@
         <v/>
       </c>
       <c r="Z7" s="42">
-        <f>INT((X7-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X7-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA7" s="42">
-        <f>IF(X7=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X7=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2261,11 +2263,11 @@
         <v/>
       </c>
       <c r="Z8" s="42">
-        <f>INT((X8-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X8-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA8" s="42">
-        <f>IF(X8=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X8=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2383,11 +2385,11 @@
         <v/>
       </c>
       <c r="Z9" s="42">
-        <f>INT((X9-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X9-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA9" s="42">
-        <f>IF(X9=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X9=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2506,11 +2508,11 @@
         <v/>
       </c>
       <c r="Z10" s="42">
-        <f>INT((X10-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X10-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA10" s="42">
-        <f>IF(X10=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X10=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2629,11 +2631,11 @@
         <v/>
       </c>
       <c r="Z11" s="42">
-        <f>INT((X11-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X11-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA11" s="42">
-        <f>IF(X11=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X11=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2750,11 +2752,11 @@
         <v/>
       </c>
       <c r="Z12" s="42">
-        <f>INT((X12-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X12-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA12" s="42">
-        <f>IF(X12=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X12=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2871,11 +2873,11 @@
         <v/>
       </c>
       <c r="Z13" s="42">
-        <f>INT((X13-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X13-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA13" s="42">
-        <f>IF(X13=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X13=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -2993,11 +2995,11 @@
         <v/>
       </c>
       <c r="Z14" s="42">
-        <f>INT((X14-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X14-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA14" s="42">
-        <f>IF(X14=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X14=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -3114,11 +3116,11 @@
         <v/>
       </c>
       <c r="Z15" s="42">
-        <f>INT((X15-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X15-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA15" s="42">
-        <f>IF(X15=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X15=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -3238,11 +3240,11 @@
         <v/>
       </c>
       <c r="Z16" s="42">
-        <f>INT((X16-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X16-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA16" s="42">
-        <f>IF(X16=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X16=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -3361,11 +3363,11 @@
         <v/>
       </c>
       <c r="Z17" s="42">
-        <f>INT((X17-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X17-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA17" s="42">
-        <f>IF(X17=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X17=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -3478,11 +3480,11 @@
         <v/>
       </c>
       <c r="Z18" s="42">
-        <f>INT((X18-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X18-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA18" s="42">
-        <f>IF(X18=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X18=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -3595,11 +3597,11 @@
         <v/>
       </c>
       <c r="Z19" s="42">
-        <f>INT((X19-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X19-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA19" s="42">
-        <f>IF(X19=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X19=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -3712,11 +3714,11 @@
         <v/>
       </c>
       <c r="Z20" s="42">
-        <f>INT((X20-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X20-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA20" s="42">
-        <f>IF(X20=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X20=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -3836,11 +3838,11 @@
         <v/>
       </c>
       <c r="Z21" s="42">
-        <f>INT((X21-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X21-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA21" s="42">
-        <f>IF(X21=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X21=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -3953,11 +3955,11 @@
         <v/>
       </c>
       <c r="Z22" s="42">
-        <f>INT((X22-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X22-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA22" s="42">
-        <f>IF(X22=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X22=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -4075,11 +4077,11 @@
         <v/>
       </c>
       <c r="Z23" s="42">
-        <f>INT((X23-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X23-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA23" s="42">
-        <f>IF(X23=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X23=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -4188,11 +4190,11 @@
         <v/>
       </c>
       <c r="Z24" s="42">
-        <f>INT((X24-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X24-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA24" s="42">
-        <f>IF(X24=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X24=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -4305,11 +4307,11 @@
         <v/>
       </c>
       <c r="Z25" s="42">
-        <f>INT((X25-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X25-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA25" s="42">
-        <f>IF(X25=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X25=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -4422,11 +4424,11 @@
         <v/>
       </c>
       <c r="Z26" s="42">
-        <f>INT((X26-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X26-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA26" s="42">
-        <f>IF(X26=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X26=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -4539,11 +4541,11 @@
         <v/>
       </c>
       <c r="Z27" s="42">
-        <f>INT((X27-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X27-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA27" s="42">
-        <f>IF(X27=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X27=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -4662,11 +4664,11 @@
         <v/>
       </c>
       <c r="Z28" s="42">
-        <f>INT((X28-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X28-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA28" s="42">
-        <f>IF(X28=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X28=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -4784,11 +4786,11 @@
         <v/>
       </c>
       <c r="Z29" s="42">
-        <f>INT((X29-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X29-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA29" s="42">
-        <f>IF(X29=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X29=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -4907,11 +4909,11 @@
         <v/>
       </c>
       <c r="Z30" s="42">
-        <f>INT((X30-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X30-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA30" s="42">
-        <f>IF(X30=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X30=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5024,11 +5026,11 @@
         <v/>
       </c>
       <c r="Z31" s="42">
-        <f>INT((X31-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X31-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA31" s="42">
-        <f>IF(X31=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X31=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5145,11 +5147,11 @@
         <v/>
       </c>
       <c r="Z32" s="42">
-        <f>INT((X32-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X32-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA32" s="42">
-        <f>IF(X32=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X32=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5266,11 +5268,11 @@
         <v/>
       </c>
       <c r="Z33" s="42">
-        <f>INT((X33-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X33-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA33" s="42">
-        <f>IF(X33=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X33=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5391,11 +5393,11 @@
         <v/>
       </c>
       <c r="Z34" s="42">
-        <f>INT((X34-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X34-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA34" s="42">
-        <f>IF(X34=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X34=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5504,11 +5506,11 @@
         <v/>
       </c>
       <c r="Z35" s="42">
-        <f>INT((X35-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X35-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA35" s="42">
-        <f>IF(X35=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X35=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5625,11 +5627,11 @@
         <v/>
       </c>
       <c r="Z36" s="42">
-        <f>INT((X36-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X36-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA36" s="42">
-        <f>IF(X36=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X36=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5742,11 +5744,11 @@
         <v/>
       </c>
       <c r="Z37" s="42">
-        <f>INT((X37-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X37-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA37" s="42">
-        <f>IF(X37=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X37=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5855,11 +5857,11 @@
         <v/>
       </c>
       <c r="Z38" s="42">
-        <f>INT((X38-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X38-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA38" s="42">
-        <f>IF(X38=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X38=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -5976,11 +5978,11 @@
         <v/>
       </c>
       <c r="Z39" s="42">
-        <f>INT((X39-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X39-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA39" s="42">
-        <f>IF(X39=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X39=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -6097,11 +6099,11 @@
         <v/>
       </c>
       <c r="Z40" s="42">
-        <f>INT((X40-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X40-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA40" s="42">
-        <f>IF(X40=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X40=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -6214,11 +6216,11 @@
         <v/>
       </c>
       <c r="Z41" s="42">
-        <f>INT((X41-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X41-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA41" s="42">
-        <f>IF(X41=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X41=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -6331,11 +6333,11 @@
         <v/>
       </c>
       <c r="Z42" s="42">
-        <f>INT((X42-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X42-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA42" s="42">
-        <f>IF(X42=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X42=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -6452,11 +6454,11 @@
         <v/>
       </c>
       <c r="Z43" s="42">
-        <f>INT((X43-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X43-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA43" s="42">
-        <f>IF(X43=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X43=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -6565,11 +6567,11 @@
         <v/>
       </c>
       <c r="Z44" s="42">
-        <f>INT((X44-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X44-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA44" s="42">
-        <f>IF(X44=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X44=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -6688,11 +6690,11 @@
         <v/>
       </c>
       <c r="Z45" s="42">
-        <f>INT((X45-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X45-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA45" s="42">
-        <f>IF(X45=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X45=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -6812,11 +6814,11 @@
         <v/>
       </c>
       <c r="Z46" s="42">
-        <f>INT((X46-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X46-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA46" s="42">
-        <f>IF(X46=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X46=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -6933,11 +6935,11 @@
         <v/>
       </c>
       <c r="Z47" s="42">
-        <f>INT((X47-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X47-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA47" s="42">
-        <f>IF(X47=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X47=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7050,11 +7052,11 @@
         <v/>
       </c>
       <c r="Z48" s="42">
-        <f>INT((X48-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X48-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA48" s="42">
-        <f>IF(X48=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X48=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7167,11 +7169,11 @@
         <v/>
       </c>
       <c r="Z49" s="42">
-        <f>INT((X49-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X49-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA49" s="42">
-        <f>IF(X49=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X49=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7288,11 +7290,11 @@
         <v/>
       </c>
       <c r="Z50" s="42">
-        <f>INT((X50-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X50-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA50" s="42">
-        <f>IF(X50=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X50=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7405,11 +7407,11 @@
         <v/>
       </c>
       <c r="Z51" s="42">
-        <f>INT((X51-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X51-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA51" s="42">
-        <f>IF(X51=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X51=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7526,11 +7528,11 @@
         <v/>
       </c>
       <c r="Z52" s="42">
-        <f>INT((X52-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X52-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA52" s="42">
-        <f>IF(X52=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X52=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7643,11 +7645,11 @@
         <v/>
       </c>
       <c r="Z53" s="42">
-        <f>INT((X53-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X53-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA53" s="42">
-        <f>IF(X53=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X53=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7760,11 +7762,11 @@
         <v/>
       </c>
       <c r="Z54" s="42">
-        <f>INT((X54-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X54-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA54" s="42">
-        <f>IF(X54=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X54=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7881,11 +7883,11 @@
         <v/>
       </c>
       <c r="Z55" s="42">
-        <f>INT((X55-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X55-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA55" s="42">
-        <f>IF(X55=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X55=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -7998,11 +8000,11 @@
         <v/>
       </c>
       <c r="Z56" s="42">
-        <f>INT((X56-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X56-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA56" s="42">
-        <f>IF(X56=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X56=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -8115,11 +8117,11 @@
         <v/>
       </c>
       <c r="Z57" s="42">
-        <f>INT((X57-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X57-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA57" s="42">
-        <f>IF(X57=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X57=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -8239,11 +8241,11 @@
         <v/>
       </c>
       <c r="Z58" s="42">
-        <f>INT((X58-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X58-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA58" s="42">
-        <f>IF(X58=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X58=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -8361,11 +8363,11 @@
         <v/>
       </c>
       <c r="Z59" s="42">
-        <f>INT((X59-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X59-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA59" s="42">
-        <f>IF(X59=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X59=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -8474,11 +8476,11 @@
         <v/>
       </c>
       <c r="Z60" s="42">
-        <f>INT((X60-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X60-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA60" s="42">
-        <f>IF(X60=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X60=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -8596,11 +8598,11 @@
         <v/>
       </c>
       <c r="Z61" s="42">
-        <f>INT((X61-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X61-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA61" s="42">
-        <f>IF(X61=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X61=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -8713,11 +8715,11 @@
         <v/>
       </c>
       <c r="Z62" s="42">
-        <f>INT((X62-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X62-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA62" s="42">
-        <f>IF(X62=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X62=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -8834,11 +8836,11 @@
         <v/>
       </c>
       <c r="Z63" s="42">
-        <f>INT((X63-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X63-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA63" s="42">
-        <f>IF(X63=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X63=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -8951,11 +8953,11 @@
         <v/>
       </c>
       <c r="Z64" s="42">
-        <f>INT((X64-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X64-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA64" s="42">
-        <f>IF(X64=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X64=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9073,11 +9075,11 @@
         <v/>
       </c>
       <c r="Z65" s="42">
-        <f>INT((X65-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X65-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA65" s="42">
-        <f>IF(X65=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X65=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9196,11 +9198,11 @@
         <v/>
       </c>
       <c r="Z66" s="42">
-        <f>INT((X66-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X66-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA66" s="42">
-        <f>IF(X66=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X66=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9309,11 +9311,11 @@
         <v/>
       </c>
       <c r="Z67" s="42">
-        <f>INT((X67-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X67-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA67" s="42">
-        <f>IF(X67=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X67=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9422,11 +9424,11 @@
         <v/>
       </c>
       <c r="Z68" s="42">
-        <f>INT((X68-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X68-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA68" s="42">
-        <f>IF(X68=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X68=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9535,11 +9537,11 @@
         <v/>
       </c>
       <c r="Z69" s="42">
-        <f>INT((X69-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X69-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA69" s="42">
-        <f>IF(X69=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X69=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9648,11 +9650,11 @@
         <v/>
       </c>
       <c r="Z70" s="42">
-        <f>INT((X70-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X70-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA70" s="42">
-        <f>IF(X70=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X70=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9765,11 +9767,11 @@
         <v/>
       </c>
       <c r="Z71" s="42">
-        <f>INT((X71-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X71-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA71" s="42">
-        <f>IF(X71=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X71=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9878,11 +9880,11 @@
         <v/>
       </c>
       <c r="Z72" s="42">
-        <f>INT((X72-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X72-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA72" s="42">
-        <f>IF(X72=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X72=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -9999,11 +10001,11 @@
         <v/>
       </c>
       <c r="Z73" s="42">
-        <f>INT((X73-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X73-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA73" s="42">
-        <f>IF(X73=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X73=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -10120,11 +10122,11 @@
         <v/>
       </c>
       <c r="Z74" s="42">
-        <f>INT((X74-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X74-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA74" s="42">
-        <f>IF(X74=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X74=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -10233,11 +10235,11 @@
         <v/>
       </c>
       <c r="Z75" s="42">
-        <f>INT((X75-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X75-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA75" s="42">
-        <f>IF(X75=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X75=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -10346,11 +10348,11 @@
         <v/>
       </c>
       <c r="Z76" s="42">
-        <f>INT((X76-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X76-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA76" s="42">
-        <f>IF(X76=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X76=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -10459,11 +10461,11 @@
         <v/>
       </c>
       <c r="Z77" s="42">
-        <f>INT((X77-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X77-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA77" s="42">
-        <f>IF(X77=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X77=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -10576,11 +10578,11 @@
         <v/>
       </c>
       <c r="Z78" s="42">
-        <f>INT((X78-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X78-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA78" s="42">
-        <f>IF(X78=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X78=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -10693,11 +10695,11 @@
         <v/>
       </c>
       <c r="Z79" s="42">
-        <f>INT((X79-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X79-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA79" s="42">
-        <f>IF(X79=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X79=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -10806,11 +10808,11 @@
         <v/>
       </c>
       <c r="Z80" s="42">
-        <f>INT((X80-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X80-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA80" s="42">
-        <f>IF(X80=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X80=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -10919,11 +10921,11 @@
         <v/>
       </c>
       <c r="Z81" s="42">
-        <f>INT((X81-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X81-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA81" s="42">
-        <f>IF(X81=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X81=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11032,11 +11034,11 @@
         <v/>
       </c>
       <c r="Z82" s="42">
-        <f>INT((X82-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X82-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA82" s="42">
-        <f>IF(X82=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X82=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11149,11 +11151,11 @@
         <v/>
       </c>
       <c r="Z83" s="42">
-        <f>INT((X83-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X83-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA83" s="42">
-        <f>IF(X83=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X83=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11262,11 +11264,11 @@
         <v/>
       </c>
       <c r="Z84" s="42">
-        <f>INT((X84-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X84-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA84" s="42">
-        <f>IF(X84=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X84=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11384,11 +11386,11 @@
         <v/>
       </c>
       <c r="Z85" s="42">
-        <f>INT((X85-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X85-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA85" s="42">
-        <f>IF(X85=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X85=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11497,11 +11499,11 @@
         <v/>
       </c>
       <c r="Z86" s="42">
-        <f>INT((X86-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X86-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA86" s="42">
-        <f>IF(X86=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X86=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11614,11 +11616,11 @@
         <v/>
       </c>
       <c r="Z87" s="42">
-        <f>INT((X87-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X87-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA87" s="42">
-        <f>IF(X87=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X87=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11731,11 +11733,11 @@
         <v/>
       </c>
       <c r="Z88" s="42">
-        <f>INT((X88-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X88-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA88" s="42">
-        <f>IF(X88=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X88=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11852,11 +11854,11 @@
         <v/>
       </c>
       <c r="Z89" s="42">
-        <f>INT((X89-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X89-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA89" s="42">
-        <f>IF(X89=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X89=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -11969,11 +11971,11 @@
         <v/>
       </c>
       <c r="Z90" s="42">
-        <f>INT((X90-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X90-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA90" s="42">
-        <f>IF(X90=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X90=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -12082,11 +12084,11 @@
         <v/>
       </c>
       <c r="Z91" s="42">
-        <f>INT((X91-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X91-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA91" s="42">
-        <f>IF(X91=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X91=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -12199,11 +12201,11 @@
         <v/>
       </c>
       <c r="Z92" s="42">
-        <f>INT((X92-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X92-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA92" s="42">
-        <f>IF(X92=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X92=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -12320,11 +12322,11 @@
         <v/>
       </c>
       <c r="Z93" s="42">
-        <f>INT((X93-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X93-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA93" s="42">
-        <f>IF(X93=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X93=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -12433,11 +12435,11 @@
         <v/>
       </c>
       <c r="Z94" s="42">
-        <f>INT((X94-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X94-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA94" s="42">
-        <f>IF(X94=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X94=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -12556,11 +12558,11 @@
         <v/>
       </c>
       <c r="Z95" s="42">
-        <f>INT((X95-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X95-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA95" s="42">
-        <f>IF(X95=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X95=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -12673,11 +12675,11 @@
         <v/>
       </c>
       <c r="Z96" s="42">
-        <f>INT((X96-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X96-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA96" s="42">
-        <f>IF(X96=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X96=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -12797,11 +12799,11 @@
         <v/>
       </c>
       <c r="Z97" s="42">
-        <f>INT((X97-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X97-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA97" s="42">
-        <f>IF(X97=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X97=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -12910,11 +12912,11 @@
         <v/>
       </c>
       <c r="Z98" s="42">
-        <f>INT((X98-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X98-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA98" s="42">
-        <f>IF(X98=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X98=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -13023,11 +13025,11 @@
         <v/>
       </c>
       <c r="Z99" s="42">
-        <f>INT((X99-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X99-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA99" s="42">
-        <f>IF(X99=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X99=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -13136,11 +13138,11 @@
         <v/>
       </c>
       <c r="Z100" s="42">
-        <f>INT((X100-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X100-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA100" s="42">
-        <f>IF(X100=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X100=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -13231,7 +13233,7 @@
         <v>44</v>
       </c>
       <c r="T101" s="38">
-        <f>CHOOSE(MONTH(X101),"Ene","Feb","Mar","Abr","May","Jun","Jul","Ago","Sep","Oct","Nov","Dic")&amp;" "&amp;YEAR(X101)</f>
+        <f>CHOOSE(MONTH(X103),"Ene","Feb","Mar","Abr","May","Jun","Jul","Ago","Sep","Oct","Nov","Dic")&amp;" "&amp;YEAR(X103)</f>
         <v/>
       </c>
       <c r="U101" s="40" t="n"/>
@@ -13245,15 +13247,217 @@
         <v>46436</v>
       </c>
       <c r="Y101" s="42">
-        <f>CHOOSE(WEEKDAY(X101,2),"lunes","martes","miércoles","jueves","viernes","sábado","domingo")</f>
+        <f>CHOOSE(WEEKDAY(X103,2),"lunes","martes","miércoles","jueves","viernes","sábado","domingo")</f>
         <v/>
       </c>
       <c r="Z101" s="42">
-        <f>INT((X101-MIN($X$2:$X$101))/7)+1</f>
+        <f>INT((X103-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
       <c r="AA101" s="42">
-        <f>IF(X101=MIN($X$2:$X$101),"Lanzamiento","Calendario semanal")</f>
+        <f>IF(X103=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Editorial</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Historia de la publicidad en México</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing y contenidos</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>historia de la publicidad en méxico</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>TOFU</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Conservar el posicionamiento ya ganado de la URL original (202 clics/16m) con una versión 2026 ampliada y verificada.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Actualizar v2026 (misma URL)</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>https://www.continentalmedia.com.mx/2013/04/historia-de-la-publicidad-en-mexico/</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Migración SEO — ruta heredada, ver migracion/LEEME_transicion_seo.md §5</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing 360</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="T102">
+        <f>CHOOSE(MONTH(X102),"Ene","Feb","Mar","Abr","May","Jun","Jul","Ago","Sep","Oct","Nov","Dic")&amp;" "&amp;YEAR(X102)</f>
+        <v/>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="X102" s="49" t="n">
+        <v>46322</v>
+      </c>
+      <c r="Y102">
+        <f>CHOOSE(WEEKDAY(X102,2),"lunes","martes","miércoles","jueves","viernes","sábado","domingo")</f>
+        <v/>
+      </c>
+      <c r="Z102">
+        <f>INT((X102-MIN($X$2:$X$103))/7)+1</f>
+        <v/>
+      </c>
+      <c r="AA102">
+        <f>IF(X102=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Editorial</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Pioneros de la publicidad en México</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing y contenidos</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>pioneros de la publicidad en méxico</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Informacional</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>TOFU</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Conservar el posicionamiento ya ganado de la URL original (48 clics/16m) con una versión 2026 ampliada y verificada.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>México</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Actualizar v2026 (misma URL)</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>https://www.continentalmedia.com.mx/2014/02/pioneros-de-la-publicidad-en-mexico/</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Migración SEO — ruta heredada, ver migracion/LEEME_transicion_seo.md §5</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing 360</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="T103">
+        <f>CHOOSE(MONTH(X103),"Ene","Feb","Mar","Abr","May","Jun","Jul","Ago","Sep","Oct","Nov","Dic")&amp;" "&amp;YEAR(X103)</f>
+        <v/>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>En revisión</t>
+        </is>
+      </c>
+      <c r="X103" s="49" t="n">
+        <v>46322</v>
+      </c>
+      <c r="Y103">
+        <f>CHOOSE(WEEKDAY(X103,2),"lunes","martes","miércoles","jueves","viernes","sábado","domingo")</f>
+        <v/>
+      </c>
+      <c r="Z103">
+        <f>INT((X103-MIN($X$2:$X$103))/7)+1</f>
+        <v/>
+      </c>
+      <c r="AA103">
+        <f>IF(X103=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
@@ -13363,7 +13567,7 @@
       </c>
       <c r="E2" s="38" t="n"/>
       <c r="F2" s="39">
-        <f>IF(E2="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E2,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E2="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E2,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G2" s="39" t="inlineStr">
@@ -13377,7 +13581,7 @@
         </is>
       </c>
       <c r="I2" s="43">
-        <f>IF(OR(D2="Consolidar",D2="Re-redactar v2026",D2="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E2,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D2="Consolidar",D2="Re-redactar v2026",D2="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E2,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13406,7 +13610,7 @@
         </is>
       </c>
       <c r="F3" s="39">
-        <f>IF(E3="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E3,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E3="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E3,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G3" s="39" t="inlineStr">
@@ -13420,7 +13624,7 @@
         </is>
       </c>
       <c r="I3" s="43">
-        <f>IF(OR(D3="Consolidar",D3="Re-redactar v2026",D3="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E3,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D3="Consolidar",D3="Re-redactar v2026",D3="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E3,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13449,7 +13653,7 @@
         </is>
       </c>
       <c r="F4" s="39">
-        <f>IF(E4="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E4,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E4="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E4,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G4" s="39" t="inlineStr">
@@ -13463,7 +13667,7 @@
         </is>
       </c>
       <c r="I4" s="43">
-        <f>IF(OR(D4="Consolidar",D4="Re-redactar v2026",D4="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E4,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D4="Consolidar",D4="Re-redactar v2026",D4="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E4,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13488,12 +13692,12 @@
       </c>
       <c r="E5" s="38" t="n"/>
       <c r="F5" s="39">
-        <f>IF(E5="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E5,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E5="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E5,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G5" s="39" t="inlineStr">
         <is>
-          <t>410, o 301 a /blog/ o a la categoría más cercana</t>
+          <t>301 a /blog/ (sin tema propio — ver migracion/redirects_lista_corta.csv)</t>
         </is>
       </c>
       <c r="H5" s="39" t="inlineStr">
@@ -13502,7 +13706,7 @@
         </is>
       </c>
       <c r="I5" s="43">
-        <f>IF(OR(D5="Consolidar",D5="Re-redactar v2026",D5="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E5,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D5="Consolidar",D5="Re-redactar v2026",D5="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E5,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13531,7 +13735,7 @@
         </is>
       </c>
       <c r="F6" s="39">
-        <f>IF(E6="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E6,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E6="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E6,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G6" s="39" t="inlineStr">
@@ -13545,7 +13749,7 @@
         </is>
       </c>
       <c r="I6" s="43">
-        <f>IF(OR(D6="Consolidar",D6="Re-redactar v2026",D6="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E6,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D6="Consolidar",D6="Re-redactar v2026",D6="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E6,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13574,7 +13778,7 @@
         </is>
       </c>
       <c r="F7" s="39">
-        <f>IF(E7="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E7,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E7="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E7,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G7" s="39" t="inlineStr">
@@ -13588,7 +13792,7 @@
         </is>
       </c>
       <c r="I7" s="43">
-        <f>IF(OR(D7="Consolidar",D7="Re-redactar v2026",D7="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E7,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D7="Consolidar",D7="Re-redactar v2026",D7="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E7,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13617,7 +13821,7 @@
         </is>
       </c>
       <c r="F8" s="39">
-        <f>IF(E8="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E8,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E8="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E8,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G8" s="39" t="inlineStr">
@@ -13631,7 +13835,7 @@
         </is>
       </c>
       <c r="I8" s="43">
-        <f>IF(OR(D8="Consolidar",D8="Re-redactar v2026",D8="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E8,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D8="Consolidar",D8="Re-redactar v2026",D8="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E8,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13660,7 +13864,7 @@
         </is>
       </c>
       <c r="F9" s="39">
-        <f>IF(E9="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E9,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E9="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E9,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G9" s="39" t="inlineStr">
@@ -13674,7 +13878,7 @@
         </is>
       </c>
       <c r="I9" s="43">
-        <f>IF(OR(D9="Consolidar",D9="Re-redactar v2026",D9="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E9,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D9="Consolidar",D9="Re-redactar v2026",D9="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E9,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13703,7 +13907,7 @@
         </is>
       </c>
       <c r="F10" s="39">
-        <f>IF(E10="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E10,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E10="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E10,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G10" s="39" t="inlineStr">
@@ -13717,7 +13921,7 @@
         </is>
       </c>
       <c r="I10" s="43">
-        <f>IF(OR(D10="Consolidar",D10="Re-redactar v2026",D10="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E10,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D10="Consolidar",D10="Re-redactar v2026",D10="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E10,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13746,7 +13950,7 @@
         </is>
       </c>
       <c r="F11" s="39">
-        <f>IF(E11="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E11,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E11="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E11,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G11" s="39" t="inlineStr">
@@ -13760,7 +13964,7 @@
         </is>
       </c>
       <c r="I11" s="43">
-        <f>IF(OR(D11="Consolidar",D11="Re-redactar v2026",D11="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E11,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D11="Consolidar",D11="Re-redactar v2026",D11="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E11,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13789,7 +13993,7 @@
         </is>
       </c>
       <c r="F12" s="39">
-        <f>IF(E12="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E12,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E12="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E12,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G12" s="39" t="inlineStr">
@@ -13803,7 +14007,7 @@
         </is>
       </c>
       <c r="I12" s="43">
-        <f>IF(OR(D12="Consolidar",D12="Re-redactar v2026",D12="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E12,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D12="Consolidar",D12="Re-redactar v2026",D12="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E12,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13832,7 +14036,7 @@
         </is>
       </c>
       <c r="F13" s="39">
-        <f>IF(E13="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E13,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E13="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E13,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G13" s="39" t="inlineStr">
@@ -13846,7 +14050,7 @@
         </is>
       </c>
       <c r="I13" s="43">
-        <f>IF(OR(D13="Consolidar",D13="Re-redactar v2026",D13="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E13,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D13="Consolidar",D13="Re-redactar v2026",D13="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E13,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13875,7 +14079,7 @@
         </is>
       </c>
       <c r="F14" s="39">
-        <f>IF(E14="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E14,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E14="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E14,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G14" s="39" t="inlineStr">
@@ -13889,7 +14093,7 @@
         </is>
       </c>
       <c r="I14" s="43">
-        <f>IF(OR(D14="Consolidar",D14="Re-redactar v2026",D14="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E14,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D14="Consolidar",D14="Re-redactar v2026",D14="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E14,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13918,7 +14122,7 @@
         </is>
       </c>
       <c r="F15" s="39">
-        <f>IF(E15="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E15,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E15="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E15,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G15" s="39" t="inlineStr">
@@ -13932,7 +14136,7 @@
         </is>
       </c>
       <c r="I15" s="43">
-        <f>IF(OR(D15="Consolidar",D15="Re-redactar v2026",D15="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E15,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D15="Consolidar",D15="Re-redactar v2026",D15="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E15,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -13961,7 +14165,7 @@
         </is>
       </c>
       <c r="F16" s="39">
-        <f>IF(E16="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E16,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E16="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E16,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G16" s="39" t="inlineStr">
@@ -13975,7 +14179,7 @@
         </is>
       </c>
       <c r="I16" s="43">
-        <f>IF(OR(D16="Consolidar",D16="Re-redactar v2026",D16="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E16,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D16="Consolidar",D16="Re-redactar v2026",D16="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E16,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14004,7 +14208,7 @@
         </is>
       </c>
       <c r="F17" s="39">
-        <f>IF(E17="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E17,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E17="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E17,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G17" s="39" t="inlineStr">
@@ -14018,7 +14222,7 @@
         </is>
       </c>
       <c r="I17" s="43">
-        <f>IF(OR(D17="Consolidar",D17="Re-redactar v2026",D17="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E17,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D17="Consolidar",D17="Re-redactar v2026",D17="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E17,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14047,7 +14251,7 @@
         </is>
       </c>
       <c r="F18" s="39">
-        <f>IF(E18="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E18,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E18="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E18,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G18" s="39" t="inlineStr">
@@ -14061,7 +14265,7 @@
         </is>
       </c>
       <c r="I18" s="43">
-        <f>IF(OR(D18="Consolidar",D18="Re-redactar v2026",D18="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E18,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D18="Consolidar",D18="Re-redactar v2026",D18="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E18,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14090,7 +14294,7 @@
         </is>
       </c>
       <c r="F19" s="39">
-        <f>IF(E19="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E19,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E19="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E19,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G19" s="39" t="inlineStr">
@@ -14104,7 +14308,7 @@
         </is>
       </c>
       <c r="I19" s="43">
-        <f>IF(OR(D19="Consolidar",D19="Re-redactar v2026",D19="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E19,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D19="Consolidar",D19="Re-redactar v2026",D19="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E19,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14133,7 +14337,7 @@
         </is>
       </c>
       <c r="F20" s="39">
-        <f>IF(E20="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E20,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E20="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E20,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G20" s="39" t="inlineStr">
@@ -14147,7 +14351,7 @@
         </is>
       </c>
       <c r="I20" s="43">
-        <f>IF(OR(D20="Consolidar",D20="Re-redactar v2026",D20="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E20,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D20="Consolidar",D20="Re-redactar v2026",D20="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E20,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14176,7 +14380,7 @@
         </is>
       </c>
       <c r="F21" s="39">
-        <f>IF(E21="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E21,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E21="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E21,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G21" s="39" t="inlineStr">
@@ -14190,7 +14394,7 @@
         </is>
       </c>
       <c r="I21" s="43">
-        <f>IF(OR(D21="Consolidar",D21="Re-redactar v2026",D21="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E21,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D21="Consolidar",D21="Re-redactar v2026",D21="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E21,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14215,7 +14419,7 @@
       </c>
       <c r="E22" s="38" t="n"/>
       <c r="F22" s="39">
-        <f>IF(E22="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E22,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E22="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E22,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G22" s="39" t="inlineStr">
@@ -14229,7 +14433,7 @@
         </is>
       </c>
       <c r="I22" s="43">
-        <f>IF(OR(D22="Consolidar",D22="Re-redactar v2026",D22="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E22,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D22="Consolidar",D22="Re-redactar v2026",D22="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E22,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14258,7 +14462,7 @@
         </is>
       </c>
       <c r="F23" s="39">
-        <f>IF(E23="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E23,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E23="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E23,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G23" s="39" t="inlineStr">
@@ -14272,7 +14476,7 @@
         </is>
       </c>
       <c r="I23" s="43">
-        <f>IF(OR(D23="Consolidar",D23="Re-redactar v2026",D23="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E23,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D23="Consolidar",D23="Re-redactar v2026",D23="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E23,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14297,7 +14501,7 @@
       </c>
       <c r="E24" s="38" t="n"/>
       <c r="F24" s="39">
-        <f>IF(E24="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E24,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E24="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E24,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G24" s="39" t="inlineStr">
@@ -14311,7 +14515,7 @@
         </is>
       </c>
       <c r="I24" s="43">
-        <f>IF(OR(D24="Consolidar",D24="Re-redactar v2026",D24="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E24,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D24="Consolidar",D24="Re-redactar v2026",D24="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E24,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14336,7 +14540,7 @@
       </c>
       <c r="E25" s="38" t="n"/>
       <c r="F25" s="39">
-        <f>IF(E25="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E25,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E25="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E25,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G25" s="39" t="inlineStr">
@@ -14350,7 +14554,7 @@
         </is>
       </c>
       <c r="I25" s="43">
-        <f>IF(OR(D25="Consolidar",D25="Re-redactar v2026",D25="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E25,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D25="Consolidar",D25="Re-redactar v2026",D25="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E25,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14379,7 +14583,7 @@
         </is>
       </c>
       <c r="F26" s="39">
-        <f>IF(E26="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E26,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E26="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E26,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G26" s="39" t="inlineStr">
@@ -14393,7 +14597,7 @@
         </is>
       </c>
       <c r="I26" s="43">
-        <f>IF(OR(D26="Consolidar",D26="Re-redactar v2026",D26="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E26,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D26="Consolidar",D26="Re-redactar v2026",D26="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E26,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14422,7 +14626,7 @@
         </is>
       </c>
       <c r="F27" s="39">
-        <f>IF(E27="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E27,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E27="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E27,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G27" s="39" t="inlineStr">
@@ -14436,7 +14640,7 @@
         </is>
       </c>
       <c r="I27" s="43">
-        <f>IF(OR(D27="Consolidar",D27="Re-redactar v2026",D27="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E27,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D27="Consolidar",D27="Re-redactar v2026",D27="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E27,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14465,7 +14669,7 @@
         </is>
       </c>
       <c r="F28" s="39">
-        <f>IF(E28="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E28,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E28="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E28,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G28" s="39" t="inlineStr">
@@ -14479,7 +14683,7 @@
         </is>
       </c>
       <c r="I28" s="43">
-        <f>IF(OR(D28="Consolidar",D28="Re-redactar v2026",D28="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E28,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D28="Consolidar",D28="Re-redactar v2026",D28="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E28,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14508,7 +14712,7 @@
         </is>
       </c>
       <c r="F29" s="39">
-        <f>IF(E29="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E29,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E29="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E29,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G29" s="39" t="inlineStr">
@@ -14522,7 +14726,7 @@
         </is>
       </c>
       <c r="I29" s="43">
-        <f>IF(OR(D29="Consolidar",D29="Re-redactar v2026",D29="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E29,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D29="Consolidar",D29="Re-redactar v2026",D29="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E29,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14551,7 +14755,7 @@
         </is>
       </c>
       <c r="F30" s="39">
-        <f>IF(E30="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E30,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E30="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E30,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G30" s="39" t="inlineStr">
@@ -14565,7 +14769,7 @@
         </is>
       </c>
       <c r="I30" s="43">
-        <f>IF(OR(D30="Consolidar",D30="Re-redactar v2026",D30="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E30,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D30="Consolidar",D30="Re-redactar v2026",D30="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E30,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14585,17 +14789,21 @@
       </c>
       <c r="D31" s="38" t="inlineStr">
         <is>
-          <t>Descartar</t>
-        </is>
-      </c>
-      <c r="E31" s="38" t="n"/>
+          <t>Actualizar v2026 (misma URL)</t>
+        </is>
+      </c>
+      <c r="E31" s="38" t="inlineStr">
+        <is>
+          <t>H-01</t>
+        </is>
+      </c>
       <c r="F31" s="39">
-        <f>IF(E31="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E31,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E31="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E31,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G31" s="39" t="inlineStr">
         <is>
-          <t>410, o 301 a /blog/ o a la categoría más cercana</t>
+          <t>Conservar ruta; sin 301</t>
         </is>
       </c>
       <c r="H31" s="39" t="inlineStr">
@@ -14604,7 +14812,7 @@
         </is>
       </c>
       <c r="I31" s="43">
-        <f>IF(OR(D31="Consolidar",D31="Re-redactar v2026",D31="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E31,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D31="Consolidar",D31="Re-redactar v2026",D31="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E31,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14633,7 +14841,7 @@
         </is>
       </c>
       <c r="F32" s="39">
-        <f>IF(E32="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E32,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E32="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E32,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G32" s="39" t="inlineStr">
@@ -14647,7 +14855,7 @@
         </is>
       </c>
       <c r="I32" s="43">
-        <f>IF(OR(D32="Consolidar",D32="Re-redactar v2026",D32="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E32,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D32="Consolidar",D32="Re-redactar v2026",D32="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E32,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14676,7 +14884,7 @@
         </is>
       </c>
       <c r="F33" s="39">
-        <f>IF(E33="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E33,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E33="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E33,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G33" s="39" t="inlineStr">
@@ -14690,7 +14898,7 @@
         </is>
       </c>
       <c r="I33" s="43">
-        <f>IF(OR(D33="Consolidar",D33="Re-redactar v2026",D33="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E33,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D33="Consolidar",D33="Re-redactar v2026",D33="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E33,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14719,7 +14927,7 @@
         </is>
       </c>
       <c r="F34" s="39">
-        <f>IF(E34="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E34,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E34="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E34,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G34" s="39" t="inlineStr">
@@ -14733,7 +14941,7 @@
         </is>
       </c>
       <c r="I34" s="43">
-        <f>IF(OR(D34="Consolidar",D34="Re-redactar v2026",D34="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E34,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D34="Consolidar",D34="Re-redactar v2026",D34="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E34,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14762,7 +14970,7 @@
         </is>
       </c>
       <c r="F35" s="39">
-        <f>IF(E35="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E35,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E35="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E35,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G35" s="39" t="inlineStr">
@@ -14776,7 +14984,7 @@
         </is>
       </c>
       <c r="I35" s="43">
-        <f>IF(OR(D35="Consolidar",D35="Re-redactar v2026",D35="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E35,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D35="Consolidar",D35="Re-redactar v2026",D35="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E35,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14805,7 +15013,7 @@
         </is>
       </c>
       <c r="F36" s="39">
-        <f>IF(E36="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E36,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E36="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E36,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G36" s="39" t="inlineStr">
@@ -14819,7 +15027,7 @@
         </is>
       </c>
       <c r="I36" s="43">
-        <f>IF(OR(D36="Consolidar",D36="Re-redactar v2026",D36="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E36,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D36="Consolidar",D36="Re-redactar v2026",D36="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E36,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14848,7 +15056,7 @@
         </is>
       </c>
       <c r="F37" s="39">
-        <f>IF(E37="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E37,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E37="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E37,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G37" s="39" t="inlineStr">
@@ -14862,7 +15070,7 @@
         </is>
       </c>
       <c r="I37" s="43">
-        <f>IF(OR(D37="Consolidar",D37="Re-redactar v2026",D37="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E37,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D37="Consolidar",D37="Re-redactar v2026",D37="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E37,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14891,7 +15099,7 @@
         </is>
       </c>
       <c r="F38" s="39">
-        <f>IF(E38="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E38,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E38="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E38,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G38" s="39" t="inlineStr">
@@ -14905,7 +15113,7 @@
         </is>
       </c>
       <c r="I38" s="43">
-        <f>IF(OR(D38="Consolidar",D38="Re-redactar v2026",D38="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E38,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D38="Consolidar",D38="Re-redactar v2026",D38="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E38,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14934,7 +15142,7 @@
         </is>
       </c>
       <c r="F39" s="39">
-        <f>IF(E39="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E39,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E39="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E39,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G39" s="39" t="inlineStr">
@@ -14948,7 +15156,7 @@
         </is>
       </c>
       <c r="I39" s="43">
-        <f>IF(OR(D39="Consolidar",D39="Re-redactar v2026",D39="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E39,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D39="Consolidar",D39="Re-redactar v2026",D39="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E39,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -14977,7 +15185,7 @@
         </is>
       </c>
       <c r="F40" s="39">
-        <f>IF(E40="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E40,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E40="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E40,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G40" s="39" t="inlineStr">
@@ -14991,7 +15199,7 @@
         </is>
       </c>
       <c r="I40" s="43">
-        <f>IF(OR(D40="Consolidar",D40="Re-redactar v2026",D40="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E40,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D40="Consolidar",D40="Re-redactar v2026",D40="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E40,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15020,7 +15228,7 @@
         </is>
       </c>
       <c r="F41" s="39">
-        <f>IF(E41="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E41,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E41="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E41,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G41" s="39" t="inlineStr">
@@ -15034,7 +15242,7 @@
         </is>
       </c>
       <c r="I41" s="43">
-        <f>IF(OR(D41="Consolidar",D41="Re-redactar v2026",D41="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E41,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D41="Consolidar",D41="Re-redactar v2026",D41="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E41,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15063,7 +15271,7 @@
         </is>
       </c>
       <c r="F42" s="39">
-        <f>IF(E42="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E42,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E42="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E42,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G42" s="39" t="inlineStr">
@@ -15077,7 +15285,7 @@
         </is>
       </c>
       <c r="I42" s="43">
-        <f>IF(OR(D42="Consolidar",D42="Re-redactar v2026",D42="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E42,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D42="Consolidar",D42="Re-redactar v2026",D42="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E42,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15106,7 +15314,7 @@
         </is>
       </c>
       <c r="F43" s="39">
-        <f>IF(E43="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E43,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E43="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E43,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G43" s="39" t="inlineStr">
@@ -15120,7 +15328,7 @@
         </is>
       </c>
       <c r="I43" s="43">
-        <f>IF(OR(D43="Consolidar",D43="Re-redactar v2026",D43="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E43,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D43="Consolidar",D43="Re-redactar v2026",D43="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E43,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15149,7 +15357,7 @@
         </is>
       </c>
       <c r="F44" s="39">
-        <f>IF(E44="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E44,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E44="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E44,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G44" s="39" t="inlineStr">
@@ -15163,7 +15371,7 @@
         </is>
       </c>
       <c r="I44" s="43">
-        <f>IF(OR(D44="Consolidar",D44="Re-redactar v2026",D44="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E44,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D44="Consolidar",D44="Re-redactar v2026",D44="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E44,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15188,7 +15396,7 @@
       </c>
       <c r="E45" s="38" t="n"/>
       <c r="F45" s="39">
-        <f>IF(E45="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E45,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E45="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E45,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G45" s="39" t="inlineStr">
@@ -15202,7 +15410,7 @@
         </is>
       </c>
       <c r="I45" s="43">
-        <f>IF(OR(D45="Consolidar",D45="Re-redactar v2026",D45="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E45,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D45="Consolidar",D45="Re-redactar v2026",D45="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E45,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15231,7 +15439,7 @@
         </is>
       </c>
       <c r="F46" s="39">
-        <f>IF(E46="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E46,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E46="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E46,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G46" s="39" t="inlineStr">
@@ -15245,7 +15453,7 @@
         </is>
       </c>
       <c r="I46" s="43">
-        <f>IF(OR(D46="Consolidar",D46="Re-redactar v2026",D46="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E46,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D46="Consolidar",D46="Re-redactar v2026",D46="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E46,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15274,7 +15482,7 @@
         </is>
       </c>
       <c r="F47" s="39">
-        <f>IF(E47="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E47,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E47="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E47,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G47" s="39" t="inlineStr">
@@ -15288,7 +15496,7 @@
         </is>
       </c>
       <c r="I47" s="43">
-        <f>IF(OR(D47="Consolidar",D47="Re-redactar v2026",D47="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E47,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D47="Consolidar",D47="Re-redactar v2026",D47="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E47,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15313,7 +15521,7 @@
       </c>
       <c r="E48" s="38" t="n"/>
       <c r="F48" s="39">
-        <f>IF(E48="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E48,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E48="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E48,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G48" s="39" t="inlineStr">
@@ -15327,7 +15535,7 @@
         </is>
       </c>
       <c r="I48" s="43">
-        <f>IF(OR(D48="Consolidar",D48="Re-redactar v2026",D48="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E48,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D48="Consolidar",D48="Re-redactar v2026",D48="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E48,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15356,7 +15564,7 @@
         </is>
       </c>
       <c r="F49" s="39">
-        <f>IF(E49="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E49,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E49="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E49,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G49" s="39" t="inlineStr">
@@ -15370,7 +15578,7 @@
         </is>
       </c>
       <c r="I49" s="43">
-        <f>IF(OR(D49="Consolidar",D49="Re-redactar v2026",D49="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E49,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D49="Consolidar",D49="Re-redactar v2026",D49="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E49,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15395,7 +15603,7 @@
       </c>
       <c r="E50" s="38" t="n"/>
       <c r="F50" s="39">
-        <f>IF(E50="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E50,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E50="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E50,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G50" s="39" t="inlineStr">
@@ -15409,7 +15617,7 @@
         </is>
       </c>
       <c r="I50" s="43">
-        <f>IF(OR(D50="Consolidar",D50="Re-redactar v2026",D50="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E50,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D50="Consolidar",D50="Re-redactar v2026",D50="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E50,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15434,7 +15642,7 @@
       </c>
       <c r="E51" s="38" t="n"/>
       <c r="F51" s="39">
-        <f>IF(E51="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E51,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E51="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E51,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G51" s="39" t="inlineStr">
@@ -15448,7 +15656,7 @@
         </is>
       </c>
       <c r="I51" s="43">
-        <f>IF(OR(D51="Consolidar",D51="Re-redactar v2026",D51="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E51,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D51="Consolidar",D51="Re-redactar v2026",D51="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E51,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15477,7 +15685,7 @@
         </is>
       </c>
       <c r="F52" s="39">
-        <f>IF(E52="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E52,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E52="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E52,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G52" s="39" t="inlineStr">
@@ -15491,7 +15699,7 @@
         </is>
       </c>
       <c r="I52" s="43">
-        <f>IF(OR(D52="Consolidar",D52="Re-redactar v2026",D52="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E52,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D52="Consolidar",D52="Re-redactar v2026",D52="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E52,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15520,7 +15728,7 @@
         </is>
       </c>
       <c r="F53" s="39">
-        <f>IF(E53="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E53,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E53="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E53,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G53" s="39" t="inlineStr">
@@ -15534,7 +15742,7 @@
         </is>
       </c>
       <c r="I53" s="43">
-        <f>IF(OR(D53="Consolidar",D53="Re-redactar v2026",D53="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E53,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D53="Consolidar",D53="Re-redactar v2026",D53="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E53,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15563,7 +15771,7 @@
         </is>
       </c>
       <c r="F54" s="39">
-        <f>IF(E54="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E54,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E54="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E54,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G54" s="39" t="inlineStr">
@@ -15577,7 +15785,7 @@
         </is>
       </c>
       <c r="I54" s="43">
-        <f>IF(OR(D54="Consolidar",D54="Re-redactar v2026",D54="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E54,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D54="Consolidar",D54="Re-redactar v2026",D54="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E54,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15606,7 +15814,7 @@
         </is>
       </c>
       <c r="F55" s="39">
-        <f>IF(E55="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E55,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E55="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E55,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G55" s="39" t="inlineStr">
@@ -15620,7 +15828,7 @@
         </is>
       </c>
       <c r="I55" s="43">
-        <f>IF(OR(D55="Consolidar",D55="Re-redactar v2026",D55="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E55,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D55="Consolidar",D55="Re-redactar v2026",D55="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E55,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15645,7 +15853,7 @@
       </c>
       <c r="E56" s="38" t="n"/>
       <c r="F56" s="39">
-        <f>IF(E56="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E56,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E56="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E56,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G56" s="39" t="inlineStr">
@@ -15659,7 +15867,7 @@
         </is>
       </c>
       <c r="I56" s="43">
-        <f>IF(OR(D56="Consolidar",D56="Re-redactar v2026",D56="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E56,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D56="Consolidar",D56="Re-redactar v2026",D56="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E56,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15688,7 +15896,7 @@
         </is>
       </c>
       <c r="F57" s="39">
-        <f>IF(E57="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E57,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E57="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E57,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G57" s="39" t="inlineStr">
@@ -15702,7 +15910,7 @@
         </is>
       </c>
       <c r="I57" s="43">
-        <f>IF(OR(D57="Consolidar",D57="Re-redactar v2026",D57="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E57,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D57="Consolidar",D57="Re-redactar v2026",D57="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E57,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15731,7 +15939,7 @@
         </is>
       </c>
       <c r="F58" s="39">
-        <f>IF(E58="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E58,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E58="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E58,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G58" s="39" t="inlineStr">
@@ -15745,7 +15953,7 @@
         </is>
       </c>
       <c r="I58" s="43">
-        <f>IF(OR(D58="Consolidar",D58="Re-redactar v2026",D58="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E58,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D58="Consolidar",D58="Re-redactar v2026",D58="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E58,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15774,7 +15982,7 @@
         </is>
       </c>
       <c r="F59" s="39">
-        <f>IF(E59="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E59,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E59="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E59,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G59" s="39" t="inlineStr">
@@ -15788,7 +15996,7 @@
         </is>
       </c>
       <c r="I59" s="43">
-        <f>IF(OR(D59="Consolidar",D59="Re-redactar v2026",D59="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E59,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D59="Consolidar",D59="Re-redactar v2026",D59="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E59,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15817,7 +16025,7 @@
         </is>
       </c>
       <c r="F60" s="39">
-        <f>IF(E60="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E60,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E60="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E60,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G60" s="39" t="inlineStr">
@@ -15831,7 +16039,7 @@
         </is>
       </c>
       <c r="I60" s="43">
-        <f>IF(OR(D60="Consolidar",D60="Re-redactar v2026",D60="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E60,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D60="Consolidar",D60="Re-redactar v2026",D60="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E60,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15860,7 +16068,7 @@
         </is>
       </c>
       <c r="F61" s="39">
-        <f>IF(E61="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E61,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E61="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E61,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G61" s="39" t="inlineStr">
@@ -15874,7 +16082,7 @@
         </is>
       </c>
       <c r="I61" s="43">
-        <f>IF(OR(D61="Consolidar",D61="Re-redactar v2026",D61="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E61,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D61="Consolidar",D61="Re-redactar v2026",D61="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E61,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15899,12 +16107,12 @@
       </c>
       <c r="E62" s="38" t="n"/>
       <c r="F62" s="39">
-        <f>IF(E62="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E62,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E62="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E62,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G62" s="39" t="inlineStr">
         <is>
-          <t>410, o 301 a /blog/ o a la categoría más cercana</t>
+          <t>301 a /blog/ (sin tema propio — ver migracion/redirects_lista_corta.csv)</t>
         </is>
       </c>
       <c r="H62" s="39" t="inlineStr">
@@ -15913,7 +16121,7 @@
         </is>
       </c>
       <c r="I62" s="43">
-        <f>IF(OR(D62="Consolidar",D62="Re-redactar v2026",D62="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E62,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D62="Consolidar",D62="Re-redactar v2026",D62="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E62,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15942,7 +16150,7 @@
         </is>
       </c>
       <c r="F63" s="39">
-        <f>IF(E63="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E63,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E63="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E63,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G63" s="39" t="inlineStr">
@@ -15956,7 +16164,7 @@
         </is>
       </c>
       <c r="I63" s="43">
-        <f>IF(OR(D63="Consolidar",D63="Re-redactar v2026",D63="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E63,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D63="Consolidar",D63="Re-redactar v2026",D63="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E63,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -15981,7 +16189,7 @@
       </c>
       <c r="E64" s="38" t="n"/>
       <c r="F64" s="39">
-        <f>IF(E64="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E64,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E64="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E64,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G64" s="39" t="inlineStr">
@@ -15995,7 +16203,7 @@
         </is>
       </c>
       <c r="I64" s="43">
-        <f>IF(OR(D64="Consolidar",D64="Re-redactar v2026",D64="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E64,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D64="Consolidar",D64="Re-redactar v2026",D64="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E64,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16024,7 +16232,7 @@
         </is>
       </c>
       <c r="F65" s="39">
-        <f>IF(E65="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E65,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E65="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E65,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G65" s="39" t="inlineStr">
@@ -16038,7 +16246,7 @@
         </is>
       </c>
       <c r="I65" s="43">
-        <f>IF(OR(D65="Consolidar",D65="Re-redactar v2026",D65="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E65,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D65="Consolidar",D65="Re-redactar v2026",D65="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E65,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16067,7 +16275,7 @@
         </is>
       </c>
       <c r="F66" s="39">
-        <f>IF(E66="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E66,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E66="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E66,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G66" s="39" t="inlineStr">
@@ -16081,7 +16289,7 @@
         </is>
       </c>
       <c r="I66" s="43">
-        <f>IF(OR(D66="Consolidar",D66="Re-redactar v2026",D66="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E66,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D66="Consolidar",D66="Re-redactar v2026",D66="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E66,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16110,7 +16318,7 @@
         </is>
       </c>
       <c r="F67" s="39">
-        <f>IF(E67="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E67,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E67="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E67,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G67" s="39" t="inlineStr">
@@ -16124,7 +16332,7 @@
         </is>
       </c>
       <c r="I67" s="43">
-        <f>IF(OR(D67="Consolidar",D67="Re-redactar v2026",D67="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E67,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D67="Consolidar",D67="Re-redactar v2026",D67="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E67,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16149,7 +16357,7 @@
       </c>
       <c r="E68" s="38" t="n"/>
       <c r="F68" s="39">
-        <f>IF(E68="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E68,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E68="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E68,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G68" s="39" t="inlineStr">
@@ -16163,7 +16371,7 @@
         </is>
       </c>
       <c r="I68" s="43">
-        <f>IF(OR(D68="Consolidar",D68="Re-redactar v2026",D68="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E68,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D68="Consolidar",D68="Re-redactar v2026",D68="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E68,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16192,7 +16400,7 @@
         </is>
       </c>
       <c r="F69" s="39">
-        <f>IF(E69="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E69,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E69="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E69,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G69" s="39" t="inlineStr">
@@ -16206,7 +16414,7 @@
         </is>
       </c>
       <c r="I69" s="43">
-        <f>IF(OR(D69="Consolidar",D69="Re-redactar v2026",D69="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E69,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D69="Consolidar",D69="Re-redactar v2026",D69="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E69,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16226,17 +16434,21 @@
       </c>
       <c r="D70" s="38" t="inlineStr">
         <is>
-          <t>Descartar</t>
-        </is>
-      </c>
-      <c r="E70" s="38" t="n"/>
+          <t>Actualizar v2026 (misma URL)</t>
+        </is>
+      </c>
+      <c r="E70" s="38" t="inlineStr">
+        <is>
+          <t>H-02</t>
+        </is>
+      </c>
       <c r="F70" s="39">
-        <f>IF(E70="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E70,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E70="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E70,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G70" s="39" t="inlineStr">
         <is>
-          <t>410, o 301 a /blog/ o a la categoría más cercana</t>
+          <t>Conservar ruta; sin 301</t>
         </is>
       </c>
       <c r="H70" s="39" t="inlineStr">
@@ -16245,7 +16457,7 @@
         </is>
       </c>
       <c r="I70" s="43">
-        <f>IF(OR(D70="Consolidar",D70="Re-redactar v2026",D70="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E70,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D70="Consolidar",D70="Re-redactar v2026",D70="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E70,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16274,7 +16486,7 @@
         </is>
       </c>
       <c r="F71" s="39">
-        <f>IF(E71="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E71,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E71="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E71,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G71" s="39" t="inlineStr">
@@ -16288,7 +16500,7 @@
         </is>
       </c>
       <c r="I71" s="43">
-        <f>IF(OR(D71="Consolidar",D71="Re-redactar v2026",D71="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E71,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D71="Consolidar",D71="Re-redactar v2026",D71="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E71,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16317,7 +16529,7 @@
         </is>
       </c>
       <c r="F72" s="39">
-        <f>IF(E72="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E72,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E72="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E72,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G72" s="39" t="inlineStr">
@@ -16331,7 +16543,7 @@
         </is>
       </c>
       <c r="I72" s="43">
-        <f>IF(OR(D72="Consolidar",D72="Re-redactar v2026",D72="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E72,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D72="Consolidar",D72="Re-redactar v2026",D72="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E72,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16360,7 +16572,7 @@
         </is>
       </c>
       <c r="F73" s="39">
-        <f>IF(E73="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E73,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E73="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E73,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G73" s="39" t="inlineStr">
@@ -16374,7 +16586,7 @@
         </is>
       </c>
       <c r="I73" s="43">
-        <f>IF(OR(D73="Consolidar",D73="Re-redactar v2026",D73="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E73,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D73="Consolidar",D73="Re-redactar v2026",D73="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E73,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16403,7 +16615,7 @@
         </is>
       </c>
       <c r="F74" s="39">
-        <f>IF(E74="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E74,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E74="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E74,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G74" s="39" t="inlineStr">
@@ -16417,7 +16629,7 @@
         </is>
       </c>
       <c r="I74" s="43">
-        <f>IF(OR(D74="Consolidar",D74="Re-redactar v2026",D74="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E74,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D74="Consolidar",D74="Re-redactar v2026",D74="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E74,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16442,7 +16654,7 @@
       </c>
       <c r="E75" s="38" t="n"/>
       <c r="F75" s="39">
-        <f>IF(E75="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E75,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E75="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E75,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G75" s="39" t="inlineStr">
@@ -16456,7 +16668,7 @@
         </is>
       </c>
       <c r="I75" s="43">
-        <f>IF(OR(D75="Consolidar",D75="Re-redactar v2026",D75="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E75,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D75="Consolidar",D75="Re-redactar v2026",D75="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E75,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16485,7 +16697,7 @@
         </is>
       </c>
       <c r="F76" s="39">
-        <f>IF(E76="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E76,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E76="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E76,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G76" s="39" t="inlineStr">
@@ -16499,7 +16711,7 @@
         </is>
       </c>
       <c r="I76" s="43">
-        <f>IF(OR(D76="Consolidar",D76="Re-redactar v2026",D76="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E76,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D76="Consolidar",D76="Re-redactar v2026",D76="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E76,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16528,7 +16740,7 @@
         </is>
       </c>
       <c r="F77" s="39">
-        <f>IF(E77="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E77,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E77="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E77,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G77" s="39" t="inlineStr">
@@ -16542,7 +16754,7 @@
         </is>
       </c>
       <c r="I77" s="43">
-        <f>IF(OR(D77="Consolidar",D77="Re-redactar v2026",D77="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E77,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D77="Consolidar",D77="Re-redactar v2026",D77="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E77,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16567,7 +16779,7 @@
       </c>
       <c r="E78" s="38" t="n"/>
       <c r="F78" s="39">
-        <f>IF(E78="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E78,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E78="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E78,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G78" s="39" t="inlineStr">
@@ -16581,7 +16793,7 @@
         </is>
       </c>
       <c r="I78" s="43">
-        <f>IF(OR(D78="Consolidar",D78="Re-redactar v2026",D78="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E78,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D78="Consolidar",D78="Re-redactar v2026",D78="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E78,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16610,7 +16822,7 @@
         </is>
       </c>
       <c r="F79" s="39">
-        <f>IF(E79="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E79,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E79="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E79,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G79" s="39" t="inlineStr">
@@ -16624,7 +16836,7 @@
         </is>
       </c>
       <c r="I79" s="43">
-        <f>IF(OR(D79="Consolidar",D79="Re-redactar v2026",D79="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E79,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D79="Consolidar",D79="Re-redactar v2026",D79="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E79,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16653,7 +16865,7 @@
         </is>
       </c>
       <c r="F80" s="39">
-        <f>IF(E80="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E80,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E80="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E80,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G80" s="39" t="inlineStr">
@@ -16667,7 +16879,7 @@
         </is>
       </c>
       <c r="I80" s="43">
-        <f>IF(OR(D80="Consolidar",D80="Re-redactar v2026",D80="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E80,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D80="Consolidar",D80="Re-redactar v2026",D80="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E80,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16692,7 +16904,7 @@
       </c>
       <c r="E81" s="38" t="n"/>
       <c r="F81" s="39">
-        <f>IF(E81="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E81,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E81="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E81,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G81" s="39" t="inlineStr">
@@ -16706,7 +16918,7 @@
         </is>
       </c>
       <c r="I81" s="43">
-        <f>IF(OR(D81="Consolidar",D81="Re-redactar v2026",D81="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E81,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D81="Consolidar",D81="Re-redactar v2026",D81="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E81,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16731,7 +16943,7 @@
       </c>
       <c r="E82" s="38" t="n"/>
       <c r="F82" s="39">
-        <f>IF(E82="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E82,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E82="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E82,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G82" s="39" t="inlineStr">
@@ -16745,7 +16957,7 @@
         </is>
       </c>
       <c r="I82" s="43">
-        <f>IF(OR(D82="Consolidar",D82="Re-redactar v2026",D82="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E82,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D82="Consolidar",D82="Re-redactar v2026",D82="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E82,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16774,7 +16986,7 @@
         </is>
       </c>
       <c r="F83" s="39">
-        <f>IF(E83="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E83,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E83="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E83,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G83" s="39" t="inlineStr">
@@ -16788,7 +17000,7 @@
         </is>
       </c>
       <c r="I83" s="43">
-        <f>IF(OR(D83="Consolidar",D83="Re-redactar v2026",D83="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E83,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D83="Consolidar",D83="Re-redactar v2026",D83="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E83,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16817,7 +17029,7 @@
         </is>
       </c>
       <c r="F84" s="39">
-        <f>IF(E84="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E84,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E84="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E84,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G84" s="39" t="inlineStr">
@@ -16831,7 +17043,7 @@
         </is>
       </c>
       <c r="I84" s="43">
-        <f>IF(OR(D84="Consolidar",D84="Re-redactar v2026",D84="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E84,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D84="Consolidar",D84="Re-redactar v2026",D84="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E84,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16856,7 +17068,7 @@
       </c>
       <c r="E85" s="38" t="n"/>
       <c r="F85" s="39">
-        <f>IF(E85="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E85,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E85="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E85,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G85" s="39" t="inlineStr">
@@ -16870,7 +17082,7 @@
         </is>
       </c>
       <c r="I85" s="43">
-        <f>IF(OR(D85="Consolidar",D85="Re-redactar v2026",D85="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E85,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D85="Consolidar",D85="Re-redactar v2026",D85="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E85,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16899,7 +17111,7 @@
         </is>
       </c>
       <c r="F86" s="39">
-        <f>IF(E86="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E86,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E86="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E86,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G86" s="39" t="inlineStr">
@@ -16913,7 +17125,7 @@
         </is>
       </c>
       <c r="I86" s="43">
-        <f>IF(OR(D86="Consolidar",D86="Re-redactar v2026",D86="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E86,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D86="Consolidar",D86="Re-redactar v2026",D86="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E86,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16942,7 +17154,7 @@
         </is>
       </c>
       <c r="F87" s="39">
-        <f>IF(E87="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E87,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E87="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E87,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G87" s="39" t="inlineStr">
@@ -16956,7 +17168,7 @@
         </is>
       </c>
       <c r="I87" s="43">
-        <f>IF(OR(D87="Consolidar",D87="Re-redactar v2026",D87="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E87,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D87="Consolidar",D87="Re-redactar v2026",D87="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E87,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -16981,7 +17193,7 @@
       </c>
       <c r="E88" s="38" t="n"/>
       <c r="F88" s="39">
-        <f>IF(E88="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E88,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E88="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E88,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G88" s="39" t="inlineStr">
@@ -16995,7 +17207,7 @@
         </is>
       </c>
       <c r="I88" s="43">
-        <f>IF(OR(D88="Consolidar",D88="Re-redactar v2026",D88="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E88,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D88="Consolidar",D88="Re-redactar v2026",D88="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E88,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17024,7 +17236,7 @@
         </is>
       </c>
       <c r="F89" s="39">
-        <f>IF(E89="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E89,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E89="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E89,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G89" s="39" t="inlineStr">
@@ -17038,7 +17250,7 @@
         </is>
       </c>
       <c r="I89" s="43">
-        <f>IF(OR(D89="Consolidar",D89="Re-redactar v2026",D89="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E89,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D89="Consolidar",D89="Re-redactar v2026",D89="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E89,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17067,7 +17279,7 @@
         </is>
       </c>
       <c r="F90" s="39">
-        <f>IF(E90="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E90,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E90="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E90,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G90" s="39" t="inlineStr">
@@ -17081,7 +17293,7 @@
         </is>
       </c>
       <c r="I90" s="43">
-        <f>IF(OR(D90="Consolidar",D90="Re-redactar v2026",D90="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E90,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D90="Consolidar",D90="Re-redactar v2026",D90="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E90,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17110,7 +17322,7 @@
         </is>
       </c>
       <c r="F91" s="39">
-        <f>IF(E91="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E91,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E91="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E91,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G91" s="39" t="inlineStr">
@@ -17124,7 +17336,7 @@
         </is>
       </c>
       <c r="I91" s="43">
-        <f>IF(OR(D91="Consolidar",D91="Re-redactar v2026",D91="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E91,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D91="Consolidar",D91="Re-redactar v2026",D91="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E91,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17153,7 +17365,7 @@
         </is>
       </c>
       <c r="F92" s="39">
-        <f>IF(E92="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E92,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E92="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E92,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G92" s="39" t="inlineStr">
@@ -17167,7 +17379,7 @@
         </is>
       </c>
       <c r="I92" s="43">
-        <f>IF(OR(D92="Consolidar",D92="Re-redactar v2026",D92="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E92,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D92="Consolidar",D92="Re-redactar v2026",D92="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E92,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17196,7 +17408,7 @@
         </is>
       </c>
       <c r="F93" s="39">
-        <f>IF(E93="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E93,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E93="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E93,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G93" s="39" t="inlineStr">
@@ -17210,7 +17422,7 @@
         </is>
       </c>
       <c r="I93" s="43">
-        <f>IF(OR(D93="Consolidar",D93="Re-redactar v2026",D93="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E93,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D93="Consolidar",D93="Re-redactar v2026",D93="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E93,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17239,7 +17451,7 @@
         </is>
       </c>
       <c r="F94" s="39">
-        <f>IF(E94="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E94,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E94="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E94,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G94" s="39" t="inlineStr">
@@ -17253,7 +17465,7 @@
         </is>
       </c>
       <c r="I94" s="43">
-        <f>IF(OR(D94="Consolidar",D94="Re-redactar v2026",D94="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E94,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D94="Consolidar",D94="Re-redactar v2026",D94="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E94,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17282,7 +17494,7 @@
         </is>
       </c>
       <c r="F95" s="39">
-        <f>IF(E95="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E95,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E95="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E95,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G95" s="39" t="inlineStr">
@@ -17296,7 +17508,7 @@
         </is>
       </c>
       <c r="I95" s="43">
-        <f>IF(OR(D95="Consolidar",D95="Re-redactar v2026",D95="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E95,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D95="Consolidar",D95="Re-redactar v2026",D95="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E95,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17325,7 +17537,7 @@
         </is>
       </c>
       <c r="F96" s="39">
-        <f>IF(E96="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E96,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E96="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E96,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G96" s="39" t="inlineStr">
@@ -17339,7 +17551,7 @@
         </is>
       </c>
       <c r="I96" s="43">
-        <f>IF(OR(D96="Consolidar",D96="Re-redactar v2026",D96="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E96,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D96="Consolidar",D96="Re-redactar v2026",D96="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E96,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17368,7 +17580,7 @@
         </is>
       </c>
       <c r="F97" s="39">
-        <f>IF(E97="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E97,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E97="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E97,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G97" s="39" t="inlineStr">
@@ -17382,7 +17594,7 @@
         </is>
       </c>
       <c r="I97" s="43">
-        <f>IF(OR(D97="Consolidar",D97="Re-redactar v2026",D97="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E97,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D97="Consolidar",D97="Re-redactar v2026",D97="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E97,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17411,7 +17623,7 @@
         </is>
       </c>
       <c r="F98" s="39">
-        <f>IF(E98="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E98,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E98="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E98,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G98" s="39" t="inlineStr">
@@ -17425,7 +17637,7 @@
         </is>
       </c>
       <c r="I98" s="43">
-        <f>IF(OR(D98="Consolidar",D98="Re-redactar v2026",D98="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E98,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D98="Consolidar",D98="Re-redactar v2026",D98="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E98,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17454,7 +17666,7 @@
         </is>
       </c>
       <c r="F99" s="39">
-        <f>IF(E99="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E99,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E99="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E99,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G99" s="39" t="inlineStr">
@@ -17468,7 +17680,7 @@
         </is>
       </c>
       <c r="I99" s="43">
-        <f>IF(OR(D99="Consolidar",D99="Re-redactar v2026",D99="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E99,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D99="Consolidar",D99="Re-redactar v2026",D99="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E99,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17497,7 +17709,7 @@
         </is>
       </c>
       <c r="F100" s="39">
-        <f>IF(E100="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E100,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E100="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E100,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G100" s="39" t="inlineStr">
@@ -17511,7 +17723,7 @@
         </is>
       </c>
       <c r="I100" s="43">
-        <f>IF(OR(D100="Consolidar",D100="Re-redactar v2026",D100="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E100,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D100="Consolidar",D100="Re-redactar v2026",D100="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E100,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17540,7 +17752,7 @@
         </is>
       </c>
       <c r="F101" s="39">
-        <f>IF(E101="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E101,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E103="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E103,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G101" s="39" t="inlineStr">
@@ -17554,7 +17766,7 @@
         </is>
       </c>
       <c r="I101" s="43">
-        <f>IF(OR(D101="Consolidar",D101="Re-redactar v2026",D101="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E101,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D103="Consolidar",D103="Re-redactar v2026",D103="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E103,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17583,7 +17795,7 @@
         </is>
       </c>
       <c r="F102" s="39">
-        <f>IF(E102="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E102,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E102="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E102,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G102" s="39" t="inlineStr">
@@ -17597,7 +17809,7 @@
         </is>
       </c>
       <c r="I102" s="43">
-        <f>IF(OR(D102="Consolidar",D102="Re-redactar v2026",D102="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E102,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D102="Consolidar",D102="Re-redactar v2026",D102="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E102,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17626,7 +17838,7 @@
         </is>
       </c>
       <c r="F103" s="39">
-        <f>IF(E103="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E103,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E103="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E103,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G103" s="39" t="inlineStr">
@@ -17640,7 +17852,7 @@
         </is>
       </c>
       <c r="I103" s="43">
-        <f>IF(OR(D103="Consolidar",D103="Re-redactar v2026",D103="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E103,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D103="Consolidar",D103="Re-redactar v2026",D103="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E103,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17669,7 +17881,7 @@
         </is>
       </c>
       <c r="F104" s="39">
-        <f>IF(E104="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E104,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E104="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E104,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G104" s="39" t="inlineStr">
@@ -17683,7 +17895,7 @@
         </is>
       </c>
       <c r="I104" s="43">
-        <f>IF(OR(D104="Consolidar",D104="Re-redactar v2026",D104="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E104,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D104="Consolidar",D104="Re-redactar v2026",D104="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E104,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17712,7 +17924,7 @@
         </is>
       </c>
       <c r="F105" s="39">
-        <f>IF(E105="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E105,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E105="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E105,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G105" s="39" t="inlineStr">
@@ -17726,7 +17938,7 @@
         </is>
       </c>
       <c r="I105" s="43">
-        <f>IF(OR(D105="Consolidar",D105="Re-redactar v2026",D105="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E105,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D105="Consolidar",D105="Re-redactar v2026",D105="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E105,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17755,7 +17967,7 @@
         </is>
       </c>
       <c r="F106" s="39">
-        <f>IF(E106="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E106,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E106="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E106,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G106" s="39" t="inlineStr">
@@ -17769,7 +17981,7 @@
         </is>
       </c>
       <c r="I106" s="43">
-        <f>IF(OR(D106="Consolidar",D106="Re-redactar v2026",D106="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E106,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D106="Consolidar",D106="Re-redactar v2026",D106="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E106,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17798,7 +18010,7 @@
         </is>
       </c>
       <c r="F107" s="39">
-        <f>IF(E107="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E107,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E107="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E107,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G107" s="39" t="inlineStr">
@@ -17812,7 +18024,7 @@
         </is>
       </c>
       <c r="I107" s="43">
-        <f>IF(OR(D107="Consolidar",D107="Re-redactar v2026",D107="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E107,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D107="Consolidar",D107="Re-redactar v2026",D107="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E107,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17841,7 +18053,7 @@
         </is>
       </c>
       <c r="F108" s="39">
-        <f>IF(E108="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E108,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E108="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E108,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G108" s="39" t="inlineStr">
@@ -17855,7 +18067,7 @@
         </is>
       </c>
       <c r="I108" s="43">
-        <f>IF(OR(D108="Consolidar",D108="Re-redactar v2026",D108="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E108,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D108="Consolidar",D108="Re-redactar v2026",D108="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E108,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17884,7 +18096,7 @@
         </is>
       </c>
       <c r="F109" s="39">
-        <f>IF(E109="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E109,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E109="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E109,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G109" s="39" t="inlineStr">
@@ -17898,7 +18110,7 @@
         </is>
       </c>
       <c r="I109" s="43">
-        <f>IF(OR(D109="Consolidar",D109="Re-redactar v2026",D109="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E109,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D109="Consolidar",D109="Re-redactar v2026",D109="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E109,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17927,7 +18139,7 @@
         </is>
       </c>
       <c r="F110" s="39">
-        <f>IF(E110="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E110,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E110="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E110,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G110" s="39" t="inlineStr">
@@ -17941,7 +18153,7 @@
         </is>
       </c>
       <c r="I110" s="43">
-        <f>IF(OR(D110="Consolidar",D110="Re-redactar v2026",D110="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E110,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D110="Consolidar",D110="Re-redactar v2026",D110="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E110,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -17970,7 +18182,7 @@
         </is>
       </c>
       <c r="F111" s="39">
-        <f>IF(E111="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E111,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E111="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E111,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G111" s="39" t="inlineStr">
@@ -17984,7 +18196,7 @@
         </is>
       </c>
       <c r="I111" s="43">
-        <f>IF(OR(D111="Consolidar",D111="Re-redactar v2026",D111="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E111,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D111="Consolidar",D111="Re-redactar v2026",D111="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E111,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18009,7 +18221,7 @@
       </c>
       <c r="E112" s="38" t="n"/>
       <c r="F112" s="39">
-        <f>IF(E112="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E112,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E112="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E112,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G112" s="39" t="inlineStr">
@@ -18023,7 +18235,7 @@
         </is>
       </c>
       <c r="I112" s="43">
-        <f>IF(OR(D112="Consolidar",D112="Re-redactar v2026",D112="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E112,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D112="Consolidar",D112="Re-redactar v2026",D112="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E112,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18052,7 +18264,7 @@
         </is>
       </c>
       <c r="F113" s="39">
-        <f>IF(E113="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E113,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E113="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E113,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G113" s="39" t="inlineStr">
@@ -18066,7 +18278,7 @@
         </is>
       </c>
       <c r="I113" s="43">
-        <f>IF(OR(D113="Consolidar",D113="Re-redactar v2026",D113="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E113,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D113="Consolidar",D113="Re-redactar v2026",D113="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E113,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18095,7 +18307,7 @@
         </is>
       </c>
       <c r="F114" s="39">
-        <f>IF(E114="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E114,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E114="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E114,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G114" s="39" t="inlineStr">
@@ -18109,7 +18321,7 @@
         </is>
       </c>
       <c r="I114" s="43">
-        <f>IF(OR(D114="Consolidar",D114="Re-redactar v2026",D114="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E114,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D114="Consolidar",D114="Re-redactar v2026",D114="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E114,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18138,7 +18350,7 @@
         </is>
       </c>
       <c r="F115" s="39">
-        <f>IF(E115="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E115,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E115="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E115,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G115" s="39" t="inlineStr">
@@ -18152,7 +18364,7 @@
         </is>
       </c>
       <c r="I115" s="43">
-        <f>IF(OR(D115="Consolidar",D115="Re-redactar v2026",D115="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E115,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D115="Consolidar",D115="Re-redactar v2026",D115="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E115,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18181,7 +18393,7 @@
         </is>
       </c>
       <c r="F116" s="39">
-        <f>IF(E116="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E116,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E116="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E116,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G116" s="39" t="inlineStr">
@@ -18195,7 +18407,7 @@
         </is>
       </c>
       <c r="I116" s="43">
-        <f>IF(OR(D116="Consolidar",D116="Re-redactar v2026",D116="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E116,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D116="Consolidar",D116="Re-redactar v2026",D116="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E116,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18224,7 +18436,7 @@
         </is>
       </c>
       <c r="F117" s="39">
-        <f>IF(E117="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E117,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E117="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E117,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G117" s="39" t="inlineStr">
@@ -18238,7 +18450,7 @@
         </is>
       </c>
       <c r="I117" s="43">
-        <f>IF(OR(D117="Consolidar",D117="Re-redactar v2026",D117="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E117,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D117="Consolidar",D117="Re-redactar v2026",D117="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E117,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18263,7 +18475,7 @@
       </c>
       <c r="E118" s="38" t="n"/>
       <c r="F118" s="39">
-        <f>IF(E118="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E118,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E118="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E118,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G118" s="39" t="inlineStr">
@@ -18277,7 +18489,7 @@
         </is>
       </c>
       <c r="I118" s="43">
-        <f>IF(OR(D118="Consolidar",D118="Re-redactar v2026",D118="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E118,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D118="Consolidar",D118="Re-redactar v2026",D118="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E118,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18306,7 +18518,7 @@
         </is>
       </c>
       <c r="F119" s="39">
-        <f>IF(E119="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E119,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E119="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E119,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G119" s="39" t="inlineStr">
@@ -18320,7 +18532,7 @@
         </is>
       </c>
       <c r="I119" s="43">
-        <f>IF(OR(D119="Consolidar",D119="Re-redactar v2026",D119="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E119,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D119="Consolidar",D119="Re-redactar v2026",D119="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E119,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18349,7 +18561,7 @@
         </is>
       </c>
       <c r="F120" s="39">
-        <f>IF(E120="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E120,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E120="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E120,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G120" s="39" t="inlineStr">
@@ -18363,7 +18575,7 @@
         </is>
       </c>
       <c r="I120" s="43">
-        <f>IF(OR(D120="Consolidar",D120="Re-redactar v2026",D120="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E120,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D120="Consolidar",D120="Re-redactar v2026",D120="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E120,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18392,7 +18604,7 @@
         </is>
       </c>
       <c r="F121" s="39">
-        <f>IF(E121="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E121,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E121="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E121,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G121" s="39" t="inlineStr">
@@ -18406,7 +18618,7 @@
         </is>
       </c>
       <c r="I121" s="43">
-        <f>IF(OR(D121="Consolidar",D121="Re-redactar v2026",D121="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E121,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D121="Consolidar",D121="Re-redactar v2026",D121="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E121,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18435,7 +18647,7 @@
         </is>
       </c>
       <c r="F122" s="39">
-        <f>IF(E122="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E122,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E122="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E122,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G122" s="39" t="inlineStr">
@@ -18449,7 +18661,7 @@
         </is>
       </c>
       <c r="I122" s="43">
-        <f>IF(OR(D122="Consolidar",D122="Re-redactar v2026",D122="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E122,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D122="Consolidar",D122="Re-redactar v2026",D122="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E122,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18478,7 +18690,7 @@
         </is>
       </c>
       <c r="F123" s="39">
-        <f>IF(E123="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E123,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E123="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E123,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G123" s="39" t="inlineStr">
@@ -18492,7 +18704,7 @@
         </is>
       </c>
       <c r="I123" s="43">
-        <f>IF(OR(D123="Consolidar",D123="Re-redactar v2026",D123="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E123,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D123="Consolidar",D123="Re-redactar v2026",D123="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E123,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18521,7 +18733,7 @@
         </is>
       </c>
       <c r="F124" s="39">
-        <f>IF(E124="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E124,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E124="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E124,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G124" s="39" t="inlineStr">
@@ -18535,7 +18747,7 @@
         </is>
       </c>
       <c r="I124" s="43">
-        <f>IF(OR(D124="Consolidar",D124="Re-redactar v2026",D124="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E124,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D124="Consolidar",D124="Re-redactar v2026",D124="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E124,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18564,7 +18776,7 @@
         </is>
       </c>
       <c r="F125" s="39">
-        <f>IF(E125="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E125,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E125="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E125,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G125" s="39" t="inlineStr">
@@ -18578,7 +18790,7 @@
         </is>
       </c>
       <c r="I125" s="43">
-        <f>IF(OR(D125="Consolidar",D125="Re-redactar v2026",D125="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E125,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D125="Consolidar",D125="Re-redactar v2026",D125="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E125,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18607,7 +18819,7 @@
         </is>
       </c>
       <c r="F126" s="39">
-        <f>IF(E126="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E126,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E126="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E126,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G126" s="39" t="inlineStr">
@@ -18621,7 +18833,7 @@
         </is>
       </c>
       <c r="I126" s="43">
-        <f>IF(OR(D126="Consolidar",D126="Re-redactar v2026",D126="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E126,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D126="Consolidar",D126="Re-redactar v2026",D126="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E126,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18650,7 +18862,7 @@
         </is>
       </c>
       <c r="F127" s="39">
-        <f>IF(E127="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E127,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E127="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E127,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G127" s="39" t="inlineStr">
@@ -18664,7 +18876,7 @@
         </is>
       </c>
       <c r="I127" s="43">
-        <f>IF(OR(D127="Consolidar",D127="Re-redactar v2026",D127="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E127,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D127="Consolidar",D127="Re-redactar v2026",D127="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E127,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18693,7 +18905,7 @@
         </is>
       </c>
       <c r="F128" s="39">
-        <f>IF(E128="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E128,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E128="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E128,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G128" s="39" t="inlineStr">
@@ -18707,7 +18919,7 @@
         </is>
       </c>
       <c r="I128" s="43">
-        <f>IF(OR(D128="Consolidar",D128="Re-redactar v2026",D128="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E128,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D128="Consolidar",D128="Re-redactar v2026",D128="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E128,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18736,7 +18948,7 @@
         </is>
       </c>
       <c r="F129" s="39">
-        <f>IF(E129="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E129,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E129="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E129,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G129" s="39" t="inlineStr">
@@ -18750,7 +18962,7 @@
         </is>
       </c>
       <c r="I129" s="43">
-        <f>IF(OR(D129="Consolidar",D129="Re-redactar v2026",D129="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E129,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D129="Consolidar",D129="Re-redactar v2026",D129="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E129,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18779,7 +18991,7 @@
         </is>
       </c>
       <c r="F130" s="39">
-        <f>IF(E130="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E130,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E130="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E130,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G130" s="39" t="inlineStr">
@@ -18793,7 +19005,7 @@
         </is>
       </c>
       <c r="I130" s="43">
-        <f>IF(OR(D130="Consolidar",D130="Re-redactar v2026",D130="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E130,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D130="Consolidar",D130="Re-redactar v2026",D130="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E130,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18822,7 +19034,7 @@
         </is>
       </c>
       <c r="F131" s="39">
-        <f>IF(E131="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E131,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E131="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E131,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G131" s="39" t="inlineStr">
@@ -18836,7 +19048,7 @@
         </is>
       </c>
       <c r="I131" s="43">
-        <f>IF(OR(D131="Consolidar",D131="Re-redactar v2026",D131="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E131,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D131="Consolidar",D131="Re-redactar v2026",D131="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E131,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18861,7 +19073,7 @@
       </c>
       <c r="E132" s="38" t="n"/>
       <c r="F132" s="39">
-        <f>IF(E132="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E132,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E132="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E132,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G132" s="39" t="inlineStr">
@@ -18875,7 +19087,7 @@
         </is>
       </c>
       <c r="I132" s="43">
-        <f>IF(OR(D132="Consolidar",D132="Re-redactar v2026",D132="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E132,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D132="Consolidar",D132="Re-redactar v2026",D132="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E132,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18900,7 +19112,7 @@
       </c>
       <c r="E133" s="38" t="n"/>
       <c r="F133" s="39">
-        <f>IF(E133="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E133,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E133="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E133,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G133" s="39" t="inlineStr">
@@ -18914,7 +19126,7 @@
         </is>
       </c>
       <c r="I133" s="43">
-        <f>IF(OR(D133="Consolidar",D133="Re-redactar v2026",D133="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E133,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D133="Consolidar",D133="Re-redactar v2026",D133="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E133,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18943,7 +19155,7 @@
         </is>
       </c>
       <c r="F134" s="39">
-        <f>IF(E134="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E134,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E134="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E134,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G134" s="39" t="inlineStr">
@@ -18957,7 +19169,7 @@
         </is>
       </c>
       <c r="I134" s="43">
-        <f>IF(OR(D134="Consolidar",D134="Re-redactar v2026",D134="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E134,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D134="Consolidar",D134="Re-redactar v2026",D134="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E134,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -18986,7 +19198,7 @@
         </is>
       </c>
       <c r="F135" s="39">
-        <f>IF(E135="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E135,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E135="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E135,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G135" s="39" t="inlineStr">
@@ -19000,7 +19212,7 @@
         </is>
       </c>
       <c r="I135" s="43">
-        <f>IF(OR(D135="Consolidar",D135="Re-redactar v2026",D135="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E135,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D135="Consolidar",D135="Re-redactar v2026",D135="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E135,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19029,7 +19241,7 @@
         </is>
       </c>
       <c r="F136" s="39">
-        <f>IF(E136="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E136,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E136="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E136,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G136" s="39" t="inlineStr">
@@ -19043,7 +19255,7 @@
         </is>
       </c>
       <c r="I136" s="43">
-        <f>IF(OR(D136="Consolidar",D136="Re-redactar v2026",D136="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E136,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D136="Consolidar",D136="Re-redactar v2026",D136="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E136,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19072,7 +19284,7 @@
         </is>
       </c>
       <c r="F137" s="39">
-        <f>IF(E137="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E137,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E137="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E137,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G137" s="39" t="inlineStr">
@@ -19086,7 +19298,7 @@
         </is>
       </c>
       <c r="I137" s="43">
-        <f>IF(OR(D137="Consolidar",D137="Re-redactar v2026",D137="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E137,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D137="Consolidar",D137="Re-redactar v2026",D137="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E137,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19115,7 +19327,7 @@
         </is>
       </c>
       <c r="F138" s="39">
-        <f>IF(E138="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E138,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E138="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E138,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G138" s="39" t="inlineStr">
@@ -19129,7 +19341,7 @@
         </is>
       </c>
       <c r="I138" s="43">
-        <f>IF(OR(D138="Consolidar",D138="Re-redactar v2026",D138="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E138,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D138="Consolidar",D138="Re-redactar v2026",D138="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E138,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19158,7 +19370,7 @@
         </is>
       </c>
       <c r="F139" s="39">
-        <f>IF(E139="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E139,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E139="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E139,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G139" s="39" t="inlineStr">
@@ -19172,7 +19384,7 @@
         </is>
       </c>
       <c r="I139" s="43">
-        <f>IF(OR(D139="Consolidar",D139="Re-redactar v2026",D139="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E139,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D139="Consolidar",D139="Re-redactar v2026",D139="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E139,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19201,7 +19413,7 @@
         </is>
       </c>
       <c r="F140" s="39">
-        <f>IF(E140="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E140,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E140="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E140,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G140" s="39" t="inlineStr">
@@ -19215,7 +19427,7 @@
         </is>
       </c>
       <c r="I140" s="43">
-        <f>IF(OR(D140="Consolidar",D140="Re-redactar v2026",D140="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E140,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D140="Consolidar",D140="Re-redactar v2026",D140="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E140,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19244,7 +19456,7 @@
         </is>
       </c>
       <c r="F141" s="39">
-        <f>IF(E141="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E141,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E141="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E141,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G141" s="39" t="inlineStr">
@@ -19258,7 +19470,7 @@
         </is>
       </c>
       <c r="I141" s="43">
-        <f>IF(OR(D141="Consolidar",D141="Re-redactar v2026",D141="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E141,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D141="Consolidar",D141="Re-redactar v2026",D141="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E141,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19287,7 +19499,7 @@
         </is>
       </c>
       <c r="F142" s="39">
-        <f>IF(E142="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E142,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E142="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E142,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G142" s="39" t="inlineStr">
@@ -19301,7 +19513,7 @@
         </is>
       </c>
       <c r="I142" s="43">
-        <f>IF(OR(D142="Consolidar",D142="Re-redactar v2026",D142="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E142,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D142="Consolidar",D142="Re-redactar v2026",D142="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E142,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19330,7 +19542,7 @@
         </is>
       </c>
       <c r="F143" s="39">
-        <f>IF(E143="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E143,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E143="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E143,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G143" s="39" t="inlineStr">
@@ -19344,7 +19556,7 @@
         </is>
       </c>
       <c r="I143" s="43">
-        <f>IF(OR(D143="Consolidar",D143="Re-redactar v2026",D143="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E143,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D143="Consolidar",D143="Re-redactar v2026",D143="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E143,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19373,7 +19585,7 @@
         </is>
       </c>
       <c r="F144" s="39">
-        <f>IF(E144="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E144,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E144="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E144,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G144" s="39" t="inlineStr">
@@ -19387,7 +19599,7 @@
         </is>
       </c>
       <c r="I144" s="43">
-        <f>IF(OR(D144="Consolidar",D144="Re-redactar v2026",D144="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E144,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D144="Consolidar",D144="Re-redactar v2026",D144="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E144,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19416,7 +19628,7 @@
         </is>
       </c>
       <c r="F145" s="39">
-        <f>IF(E145="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E145,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E145="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E145,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G145" s="39" t="inlineStr">
@@ -19430,7 +19642,7 @@
         </is>
       </c>
       <c r="I145" s="43">
-        <f>IF(OR(D145="Consolidar",D145="Re-redactar v2026",D145="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E145,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D145="Consolidar",D145="Re-redactar v2026",D145="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E145,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19459,7 +19671,7 @@
         </is>
       </c>
       <c r="F146" s="39">
-        <f>IF(E146="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E146,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E146="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E146,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G146" s="39" t="inlineStr">
@@ -19473,7 +19685,7 @@
         </is>
       </c>
       <c r="I146" s="43">
-        <f>IF(OR(D146="Consolidar",D146="Re-redactar v2026",D146="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E146,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D146="Consolidar",D146="Re-redactar v2026",D146="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E146,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19502,7 +19714,7 @@
         </is>
       </c>
       <c r="F147" s="39">
-        <f>IF(E147="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E147,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E147="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E147,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G147" s="39" t="inlineStr">
@@ -19516,7 +19728,7 @@
         </is>
       </c>
       <c r="I147" s="43">
-        <f>IF(OR(D147="Consolidar",D147="Re-redactar v2026",D147="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E147,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D147="Consolidar",D147="Re-redactar v2026",D147="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E147,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19545,7 +19757,7 @@
         </is>
       </c>
       <c r="F148" s="39">
-        <f>IF(E148="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E148,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E148="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E148,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G148" s="39" t="inlineStr">
@@ -19559,7 +19771,7 @@
         </is>
       </c>
       <c r="I148" s="43">
-        <f>IF(OR(D148="Consolidar",D148="Re-redactar v2026",D148="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E148,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D148="Consolidar",D148="Re-redactar v2026",D148="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E148,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19588,7 +19800,7 @@
         </is>
       </c>
       <c r="F149" s="39">
-        <f>IF(E149="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E149,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E149="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E149,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G149" s="39" t="inlineStr">
@@ -19602,7 +19814,7 @@
         </is>
       </c>
       <c r="I149" s="43">
-        <f>IF(OR(D149="Consolidar",D149="Re-redactar v2026",D149="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E149,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D149="Consolidar",D149="Re-redactar v2026",D149="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E149,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19631,7 +19843,7 @@
         </is>
       </c>
       <c r="F150" s="39">
-        <f>IF(E150="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E150,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E150="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E150,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G150" s="39" t="inlineStr">
@@ -19645,7 +19857,7 @@
         </is>
       </c>
       <c r="I150" s="43">
-        <f>IF(OR(D150="Consolidar",D150="Re-redactar v2026",D150="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E150,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D150="Consolidar",D150="Re-redactar v2026",D150="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E150,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19674,7 +19886,7 @@
         </is>
       </c>
       <c r="F151" s="39">
-        <f>IF(E151="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E151,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E151="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E151,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G151" s="39" t="inlineStr">
@@ -19688,7 +19900,7 @@
         </is>
       </c>
       <c r="I151" s="43">
-        <f>IF(OR(D151="Consolidar",D151="Re-redactar v2026",D151="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E151,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D151="Consolidar",D151="Re-redactar v2026",D151="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E151,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19717,7 +19929,7 @@
         </is>
       </c>
       <c r="F152" s="39">
-        <f>IF(E152="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E152,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E152="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E152,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G152" s="39" t="inlineStr">
@@ -19731,7 +19943,7 @@
         </is>
       </c>
       <c r="I152" s="43">
-        <f>IF(OR(D152="Consolidar",D152="Re-redactar v2026",D152="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E152,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D152="Consolidar",D152="Re-redactar v2026",D152="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E152,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19760,7 +19972,7 @@
         </is>
       </c>
       <c r="F153" s="39">
-        <f>IF(E153="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E153,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E153="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E153,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G153" s="39" t="inlineStr">
@@ -19774,7 +19986,7 @@
         </is>
       </c>
       <c r="I153" s="43">
-        <f>IF(OR(D153="Consolidar",D153="Re-redactar v2026",D153="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E153,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D153="Consolidar",D153="Re-redactar v2026",D153="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E153,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19803,7 +20015,7 @@
         </is>
       </c>
       <c r="F154" s="39">
-        <f>IF(E154="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E154,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E154="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E154,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G154" s="39" t="inlineStr">
@@ -19817,7 +20029,7 @@
         </is>
       </c>
       <c r="I154" s="43">
-        <f>IF(OR(D154="Consolidar",D154="Re-redactar v2026",D154="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E154,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D154="Consolidar",D154="Re-redactar v2026",D154="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E154,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19846,7 +20058,7 @@
         </is>
       </c>
       <c r="F155" s="39">
-        <f>IF(E155="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E155,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E155="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E155,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G155" s="39" t="inlineStr">
@@ -19860,7 +20072,7 @@
         </is>
       </c>
       <c r="I155" s="43">
-        <f>IF(OR(D155="Consolidar",D155="Re-redactar v2026",D155="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E155,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D155="Consolidar",D155="Re-redactar v2026",D155="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E155,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19889,7 +20101,7 @@
         </is>
       </c>
       <c r="F156" s="39">
-        <f>IF(E156="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E156,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E156="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E156,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G156" s="39" t="inlineStr">
@@ -19903,7 +20115,7 @@
         </is>
       </c>
       <c r="I156" s="43">
-        <f>IF(OR(D156="Consolidar",D156="Re-redactar v2026",D156="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E156,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D156="Consolidar",D156="Re-redactar v2026",D156="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E156,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19928,12 +20140,12 @@
       </c>
       <c r="E157" s="38" t="n"/>
       <c r="F157" s="39">
-        <f>IF(E157="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E157,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E157="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E157,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G157" s="39" t="inlineStr">
         <is>
-          <t>410, o 301 a /blog/ o a la categoría más cercana</t>
+          <t>301 a /blog/ (sin tema propio — ver migracion/redirects_lista_corta.csv)</t>
         </is>
       </c>
       <c r="H157" s="39" t="inlineStr">
@@ -19942,7 +20154,7 @@
         </is>
       </c>
       <c r="I157" s="43">
-        <f>IF(OR(D157="Consolidar",D157="Re-redactar v2026",D157="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E157,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D157="Consolidar",D157="Re-redactar v2026",D157="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E157,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -19971,7 +20183,7 @@
         </is>
       </c>
       <c r="F158" s="39">
-        <f>IF(E158="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E158,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E158="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E158,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G158" s="39" t="inlineStr">
@@ -19985,7 +20197,7 @@
         </is>
       </c>
       <c r="I158" s="43">
-        <f>IF(OR(D158="Consolidar",D158="Re-redactar v2026",D158="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E158,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D158="Consolidar",D158="Re-redactar v2026",D158="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E158,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20014,7 +20226,7 @@
         </is>
       </c>
       <c r="F159" s="39">
-        <f>IF(E159="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E159,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E159="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E159,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G159" s="39" t="inlineStr">
@@ -20028,7 +20240,7 @@
         </is>
       </c>
       <c r="I159" s="43">
-        <f>IF(OR(D159="Consolidar",D159="Re-redactar v2026",D159="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E159,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D159="Consolidar",D159="Re-redactar v2026",D159="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E159,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20057,7 +20269,7 @@
         </is>
       </c>
       <c r="F160" s="39">
-        <f>IF(E160="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E160,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E160="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E160,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G160" s="39" t="inlineStr">
@@ -20071,7 +20283,7 @@
         </is>
       </c>
       <c r="I160" s="43">
-        <f>IF(OR(D160="Consolidar",D160="Re-redactar v2026",D160="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E160,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D160="Consolidar",D160="Re-redactar v2026",D160="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E160,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20100,7 +20312,7 @@
         </is>
       </c>
       <c r="F161" s="39">
-        <f>IF(E161="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E161,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E161="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E161,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G161" s="39" t="inlineStr">
@@ -20114,7 +20326,7 @@
         </is>
       </c>
       <c r="I161" s="43">
-        <f>IF(OR(D161="Consolidar",D161="Re-redactar v2026",D161="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E161,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D161="Consolidar",D161="Re-redactar v2026",D161="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E161,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20143,7 +20355,7 @@
         </is>
       </c>
       <c r="F162" s="39">
-        <f>IF(E162="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E162,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E162="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E162,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G162" s="39" t="inlineStr">
@@ -20157,7 +20369,7 @@
         </is>
       </c>
       <c r="I162" s="43">
-        <f>IF(OR(D162="Consolidar",D162="Re-redactar v2026",D162="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E162,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D162="Consolidar",D162="Re-redactar v2026",D162="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E162,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20186,7 +20398,7 @@
         </is>
       </c>
       <c r="F163" s="39">
-        <f>IF(E163="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E163,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E163="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E163,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G163" s="39" t="inlineStr">
@@ -20200,7 +20412,7 @@
         </is>
       </c>
       <c r="I163" s="43">
-        <f>IF(OR(D163="Consolidar",D163="Re-redactar v2026",D163="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E163,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D163="Consolidar",D163="Re-redactar v2026",D163="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E163,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20229,7 +20441,7 @@
         </is>
       </c>
       <c r="F164" s="39">
-        <f>IF(E164="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E164,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E164="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E164,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G164" s="39" t="inlineStr">
@@ -20243,7 +20455,7 @@
         </is>
       </c>
       <c r="I164" s="43">
-        <f>IF(OR(D164="Consolidar",D164="Re-redactar v2026",D164="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E164,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D164="Consolidar",D164="Re-redactar v2026",D164="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E164,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20268,7 +20480,7 @@
       </c>
       <c r="E165" s="38" t="n"/>
       <c r="F165" s="39">
-        <f>IF(E165="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E165,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E165="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E165,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G165" s="39" t="inlineStr">
@@ -20282,7 +20494,7 @@
         </is>
       </c>
       <c r="I165" s="43">
-        <f>IF(OR(D165="Consolidar",D165="Re-redactar v2026",D165="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E165,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D165="Consolidar",D165="Re-redactar v2026",D165="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E165,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20307,7 +20519,7 @@
       </c>
       <c r="E166" s="38" t="n"/>
       <c r="F166" s="39">
-        <f>IF(E166="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E166,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E166="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E166,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G166" s="39" t="inlineStr">
@@ -20321,7 +20533,7 @@
         </is>
       </c>
       <c r="I166" s="43">
-        <f>IF(OR(D166="Consolidar",D166="Re-redactar v2026",D166="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E166,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D166="Consolidar",D166="Re-redactar v2026",D166="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E166,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20346,7 +20558,7 @@
       </c>
       <c r="E167" s="38" t="n"/>
       <c r="F167" s="39">
-        <f>IF(E167="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E167,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E167="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E167,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G167" s="39" t="inlineStr">
@@ -20360,7 +20572,7 @@
         </is>
       </c>
       <c r="I167" s="43">
-        <f>IF(OR(D167="Consolidar",D167="Re-redactar v2026",D167="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E167,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D167="Consolidar",D167="Re-redactar v2026",D167="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E167,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20389,7 +20601,7 @@
         </is>
       </c>
       <c r="F168" s="39">
-        <f>IF(E168="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E168,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E168="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E168,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G168" s="39" t="inlineStr">
@@ -20403,7 +20615,7 @@
         </is>
       </c>
       <c r="I168" s="43">
-        <f>IF(OR(D168="Consolidar",D168="Re-redactar v2026",D168="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E168,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D168="Consolidar",D168="Re-redactar v2026",D168="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E168,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20432,7 +20644,7 @@
         </is>
       </c>
       <c r="F169" s="39">
-        <f>IF(E169="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E169,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E169="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E169,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G169" s="39" t="inlineStr">
@@ -20446,7 +20658,7 @@
         </is>
       </c>
       <c r="I169" s="43">
-        <f>IF(OR(D169="Consolidar",D169="Re-redactar v2026",D169="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E169,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D169="Consolidar",D169="Re-redactar v2026",D169="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E169,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20475,7 +20687,7 @@
         </is>
       </c>
       <c r="F170" s="39">
-        <f>IF(E170="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E170,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E170="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E170,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G170" s="39" t="inlineStr">
@@ -20489,7 +20701,7 @@
         </is>
       </c>
       <c r="I170" s="43">
-        <f>IF(OR(D170="Consolidar",D170="Re-redactar v2026",D170="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E170,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D170="Consolidar",D170="Re-redactar v2026",D170="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E170,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20518,7 +20730,7 @@
         </is>
       </c>
       <c r="F171" s="39">
-        <f>IF(E171="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E171,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E171="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E171,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G171" s="39" t="inlineStr">
@@ -20532,7 +20744,7 @@
         </is>
       </c>
       <c r="I171" s="43">
-        <f>IF(OR(D171="Consolidar",D171="Re-redactar v2026",D171="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E171,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D171="Consolidar",D171="Re-redactar v2026",D171="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E171,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20561,7 +20773,7 @@
         </is>
       </c>
       <c r="F172" s="39">
-        <f>IF(E172="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E172,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E172="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E172,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G172" s="39" t="inlineStr">
@@ -20575,7 +20787,7 @@
         </is>
       </c>
       <c r="I172" s="43">
-        <f>IF(OR(D172="Consolidar",D172="Re-redactar v2026",D172="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E172,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D172="Consolidar",D172="Re-redactar v2026",D172="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E172,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20604,7 +20816,7 @@
         </is>
       </c>
       <c r="F173" s="39">
-        <f>IF(E173="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E173,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E173="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E173,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G173" s="39" t="inlineStr">
@@ -20618,7 +20830,7 @@
         </is>
       </c>
       <c r="I173" s="43">
-        <f>IF(OR(D173="Consolidar",D173="Re-redactar v2026",D173="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E173,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D173="Consolidar",D173="Re-redactar v2026",D173="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E173,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20647,7 +20859,7 @@
         </is>
       </c>
       <c r="F174" s="39">
-        <f>IF(E174="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E174,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E174="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E174,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G174" s="39" t="inlineStr">
@@ -20661,7 +20873,7 @@
         </is>
       </c>
       <c r="I174" s="43">
-        <f>IF(OR(D174="Consolidar",D174="Re-redactar v2026",D174="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E174,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D174="Consolidar",D174="Re-redactar v2026",D174="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E174,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20690,7 +20902,7 @@
         </is>
       </c>
       <c r="F175" s="39">
-        <f>IF(E175="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E175,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E175="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E175,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G175" s="39" t="inlineStr">
@@ -20704,7 +20916,7 @@
         </is>
       </c>
       <c r="I175" s="43">
-        <f>IF(OR(D175="Consolidar",D175="Re-redactar v2026",D175="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E175,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D175="Consolidar",D175="Re-redactar v2026",D175="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E175,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20733,7 +20945,7 @@
         </is>
       </c>
       <c r="F176" s="39">
-        <f>IF(E176="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E176,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E176="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E176,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G176" s="39" t="inlineStr">
@@ -20747,7 +20959,7 @@
         </is>
       </c>
       <c r="I176" s="43">
-        <f>IF(OR(D176="Consolidar",D176="Re-redactar v2026",D176="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E176,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D176="Consolidar",D176="Re-redactar v2026",D176="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E176,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20776,7 +20988,7 @@
         </is>
       </c>
       <c r="F177" s="39">
-        <f>IF(E177="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E177,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E177="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E177,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G177" s="39" t="inlineStr">
@@ -20790,7 +21002,7 @@
         </is>
       </c>
       <c r="I177" s="43">
-        <f>IF(OR(D177="Consolidar",D177="Re-redactar v2026",D177="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E177,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D177="Consolidar",D177="Re-redactar v2026",D177="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E177,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20819,7 +21031,7 @@
         </is>
       </c>
       <c r="F178" s="39">
-        <f>IF(E178="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E178,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E178="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E178,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G178" s="39" t="inlineStr">
@@ -20833,7 +21045,7 @@
         </is>
       </c>
       <c r="I178" s="43">
-        <f>IF(OR(D178="Consolidar",D178="Re-redactar v2026",D178="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E178,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D178="Consolidar",D178="Re-redactar v2026",D178="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E178,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20862,7 +21074,7 @@
         </is>
       </c>
       <c r="F179" s="39">
-        <f>IF(E179="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E179,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E179="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E179,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G179" s="39" t="inlineStr">
@@ -20876,7 +21088,7 @@
         </is>
       </c>
       <c r="I179" s="43">
-        <f>IF(OR(D179="Consolidar",D179="Re-redactar v2026",D179="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E179,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D179="Consolidar",D179="Re-redactar v2026",D179="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E179,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20905,7 +21117,7 @@
         </is>
       </c>
       <c r="F180" s="39">
-        <f>IF(E180="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E180,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E180="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E180,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G180" s="39" t="inlineStr">
@@ -20919,7 +21131,7 @@
         </is>
       </c>
       <c r="I180" s="43">
-        <f>IF(OR(D180="Consolidar",D180="Re-redactar v2026",D180="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E180,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D180="Consolidar",D180="Re-redactar v2026",D180="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E180,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20948,7 +21160,7 @@
         </is>
       </c>
       <c r="F181" s="39">
-        <f>IF(E181="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E181,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E181="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E181,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G181" s="39" t="inlineStr">
@@ -20962,7 +21174,7 @@
         </is>
       </c>
       <c r="I181" s="43">
-        <f>IF(OR(D181="Consolidar",D181="Re-redactar v2026",D181="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E181,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D181="Consolidar",D181="Re-redactar v2026",D181="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E181,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -20991,7 +21203,7 @@
         </is>
       </c>
       <c r="F182" s="39">
-        <f>IF(E182="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E182,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E182="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E182,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G182" s="39" t="inlineStr">
@@ -21005,7 +21217,7 @@
         </is>
       </c>
       <c r="I182" s="43">
-        <f>IF(OR(D182="Consolidar",D182="Re-redactar v2026",D182="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E182,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D182="Consolidar",D182="Re-redactar v2026",D182="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E182,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -21034,7 +21246,7 @@
         </is>
       </c>
       <c r="F183" s="39">
-        <f>IF(E183="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E183,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E183="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E183,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G183" s="39" t="inlineStr">
@@ -21048,7 +21260,7 @@
         </is>
       </c>
       <c r="I183" s="43">
-        <f>IF(OR(D183="Consolidar",D183="Re-redactar v2026",D183="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E183,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D183="Consolidar",D183="Re-redactar v2026",D183="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E183,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -21077,7 +21289,7 @@
         </is>
       </c>
       <c r="F184" s="39">
-        <f>IF(E184="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E184,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E184="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E184,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G184" s="39" t="inlineStr">
@@ -21091,7 +21303,7 @@
         </is>
       </c>
       <c r="I184" s="43">
-        <f>IF(OR(D184="Consolidar",D184="Re-redactar v2026",D184="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E184,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D184="Consolidar",D184="Re-redactar v2026",D184="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E184,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -21120,7 +21332,7 @@
         </is>
       </c>
       <c r="F185" s="39">
-        <f>IF(E185="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E185,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E185="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E185,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G185" s="39" t="inlineStr">
@@ -21134,7 +21346,7 @@
         </is>
       </c>
       <c r="I185" s="43">
-        <f>IF(OR(D185="Consolidar",D185="Re-redactar v2026",D185="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E185,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D185="Consolidar",D185="Re-redactar v2026",D185="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E185,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -21163,7 +21375,7 @@
         </is>
       </c>
       <c r="F186" s="39">
-        <f>IF(E186="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E186,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E186="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E186,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G186" s="39" t="inlineStr">
@@ -21177,7 +21389,7 @@
         </is>
       </c>
       <c r="I186" s="43">
-        <f>IF(OR(D186="Consolidar",D186="Re-redactar v2026",D186="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E186,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D186="Consolidar",D186="Re-redactar v2026",D186="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E186,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -21206,7 +21418,7 @@
         </is>
       </c>
       <c r="F187" s="39">
-        <f>IF(E187="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E187,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E187="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E187,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G187" s="39" t="inlineStr">
@@ -21220,7 +21432,7 @@
         </is>
       </c>
       <c r="I187" s="43">
-        <f>IF(OR(D187="Consolidar",D187="Re-redactar v2026",D187="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E187,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D187="Consolidar",D187="Re-redactar v2026",D187="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E187,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -21249,7 +21461,7 @@
         </is>
       </c>
       <c r="F188" s="39">
-        <f>IF(E188="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E188,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E188="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E188,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G188" s="39" t="inlineStr">
@@ -21263,7 +21475,7 @@
         </is>
       </c>
       <c r="I188" s="43">
-        <f>IF(OR(D188="Consolidar",D188="Re-redactar v2026",D188="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E188,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D188="Consolidar",D188="Re-redactar v2026",D188="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E188,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -21286,7 +21498,7 @@
       </c>
       <c r="E189" s="38" t="n"/>
       <c r="F189" s="39">
-        <f>IF(E189="","",IFERROR(INDEX(Backlog!$C$2:$C$101,MATCH(E189,Backlog!$A$2:$A$101,0)),""))</f>
+        <f>IF(E189="","",IFERROR(INDEX(Backlog!$C$2:$C$103,MATCH(E189,Backlog!$A$2:$A$103,0)),""))</f>
         <v/>
       </c>
       <c r="G189" s="39" t="inlineStr">
@@ -21300,7 +21512,7 @@
         </is>
       </c>
       <c r="I189" s="43">
-        <f>IF(OR(D189="Consolidar",D189="Re-redactar v2026",D189="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$101,MATCH(E189,Backlog!$A$2:$A$101,0)),""),"")</f>
+        <f>IF(OR(D189="Consolidar",D189="Re-redactar v2026",D189="Actualizar v2026"),IFERROR(INDEX(Backlog!$X$2:$X$103,MATCH(E189,Backlog!$A$2:$A$103,0)),""),"")</f>
         <v/>
       </c>
     </row>
@@ -26629,11 +26841,11 @@
         </is>
       </c>
       <c r="D2" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B2,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B2,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E2" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B2,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B2,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F2" s="38">
@@ -26658,11 +26870,11 @@
         </is>
       </c>
       <c r="D3" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B3,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B3,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E3" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B3,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B3,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F3" s="38">
@@ -26687,11 +26899,11 @@
         </is>
       </c>
       <c r="D4" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B4,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B4,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E4" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B4,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B4,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F4" s="38">
@@ -26716,11 +26928,11 @@
         </is>
       </c>
       <c r="D5" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B5,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B5,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E5" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B5,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B5,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F5" s="38">
@@ -26745,11 +26957,11 @@
         </is>
       </c>
       <c r="D6" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B6,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B6,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E6" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B6,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B6,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F6" s="38">
@@ -26774,11 +26986,11 @@
         </is>
       </c>
       <c r="D7" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B7,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B7,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E7" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B7,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B7,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F7" s="38">
@@ -26803,11 +27015,11 @@
         </is>
       </c>
       <c r="D8" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B8,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B8,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E8" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B8,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B8,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F8" s="38">
@@ -26832,11 +27044,11 @@
         </is>
       </c>
       <c r="D9" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B9,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B9,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E9" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B9,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B9,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F9" s="38">
@@ -26861,11 +27073,11 @@
         </is>
       </c>
       <c r="D10" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B10,Backlog!$B$2:$B$101,"Editorial")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B10,Backlog!$B$2:$B$103,"Editorial")</f>
         <v/>
       </c>
       <c r="E10" s="38">
-        <f>COUNTIFS(Backlog!$D$2:$D$101,B10,Backlog!$B$2:$B$101,"Guía práctica")</f>
+        <f>COUNTIFS(Backlog!$D$2:$D$103,B10,Backlog!$B$2:$B$103,"Guía práctica")</f>
         <v/>
       </c>
       <c r="F10" s="38">
@@ -26894,6 +27106,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="28">
       <c r="A13" s="30" t="inlineStr">
         <is>
@@ -26966,7 +27179,7 @@
       </c>
       <c r="C5" s="36" t="inlineStr">
         <is>
-          <t>Identificador único. E-xx = editorial, G-xx = guía práctica. Es la llave para Cruces y Posts actuales.</t>
+          <t>Identificador único. E-xx = editorial, G-xx = guía práctica. Es la llave para Cruces y Posts actuales. H-xx = fuera del esquema 1-100: URL heredada conservada en su propia ruta (migración SEO, ver migracion/LEEME_transicion_seo.md), no entra al calendario martes/jueves.</t>
         </is>
       </c>
     </row>

--- a/content/blog/Backlog_Blog_Continental_Media.xlsx
+++ b/content/blog/Backlog_Blog_Continental_Media.xlsx
@@ -13260,203 +13260,203 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="27" t="inlineStr">
         <is>
           <t>H-01</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="27" t="inlineStr">
         <is>
           <t>Editorial</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="27" t="inlineStr">
         <is>
           <t>Historia de la publicidad en México</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D102" s="27" t="inlineStr">
         <is>
           <t>Estrategia de marketing y contenidos</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" s="27" t="inlineStr">
         <is>
           <t>historia de la publicidad en méxico</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="27" t="inlineStr">
         <is>
           <t>Informacional</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G102" s="27" t="inlineStr">
         <is>
           <t>TOFU</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H102" s="27" t="inlineStr">
         <is>
           <t>Conservar el posicionamiento ya ganado de la URL original (202 clics/16m) con una versión 2026 ampliada y verificada.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J102" s="27" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K102" s="27" t="inlineStr">
         <is>
           <t>Actualizar v2026 (misma URL)</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="L102" s="27" t="inlineStr">
         <is>
           <t>https://www.continentalmedia.com.mx/2013/04/historia-de-la-publicidad-en-mexico/</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr">
+      <c r="N102" s="27" t="inlineStr">
         <is>
           <t>Migración SEO — ruta heredada, ver migracion/LEEME_transicion_seo.md §5</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr">
+      <c r="P102" s="27" t="inlineStr">
         <is>
           <t>Estrategia de marketing 360</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="R102" s="27" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="T102">
+      <c r="T102" s="27">
         <f>CHOOSE(MONTH(X102),"Ene","Feb","Mar","Abr","May","Jun","Jul","Ago","Sep","Oct","Nov","Dic")&amp;" "&amp;YEAR(X102)</f>
         <v/>
       </c>
-      <c r="W102" t="inlineStr">
-        <is>
-          <t>En revisión</t>
+      <c r="W102" s="27" t="inlineStr">
+        <is>
+          <t>Publicado</t>
         </is>
       </c>
       <c r="X102" s="49" t="n">
         <v>46322</v>
       </c>
-      <c r="Y102">
+      <c r="Y102" s="27">
         <f>CHOOSE(WEEKDAY(X102,2),"lunes","martes","miércoles","jueves","viernes","sábado","domingo")</f>
         <v/>
       </c>
-      <c r="Z102">
+      <c r="Z102" s="27">
         <f>INT((X102-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
-      <c r="AA102">
+      <c r="AA102" s="27">
         <f>IF(X102=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="27" t="inlineStr">
         <is>
           <t>H-02</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="27" t="inlineStr">
         <is>
           <t>Editorial</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="27" t="inlineStr">
         <is>
           <t>Pioneros de la publicidad en México</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D103" s="27" t="inlineStr">
         <is>
           <t>Estrategia de marketing y contenidos</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" s="27" t="inlineStr">
         <is>
           <t>pioneros de la publicidad en méxico</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="27" t="inlineStr">
         <is>
           <t>Informacional</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G103" s="27" t="inlineStr">
         <is>
           <t>TOFU</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H103" s="27" t="inlineStr">
         <is>
           <t>Conservar el posicionamiento ya ganado de la URL original (48 clics/16m) con una versión 2026 ampliada y verificada.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" s="27" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J103" s="27" t="inlineStr">
         <is>
           <t>México</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K103" s="27" t="inlineStr">
         <is>
           <t>Actualizar v2026 (misma URL)</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="L103" s="27" t="inlineStr">
         <is>
           <t>https://www.continentalmedia.com.mx/2014/02/pioneros-de-la-publicidad-en-mexico/</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr">
+      <c r="N103" s="27" t="inlineStr">
         <is>
           <t>Migración SEO — ruta heredada, ver migracion/LEEME_transicion_seo.md §5</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="P103" s="27" t="inlineStr">
         <is>
           <t>Estrategia de marketing 360</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="R103" s="27" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="T103">
+      <c r="T103" s="27">
         <f>CHOOSE(MONTH(X103),"Ene","Feb","Mar","Abr","May","Jun","Jul","Ago","Sep","Oct","Nov","Dic")&amp;" "&amp;YEAR(X103)</f>
         <v/>
       </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>En revisión</t>
+      <c r="W103" s="27" t="inlineStr">
+        <is>
+          <t>Publicado</t>
         </is>
       </c>
       <c r="X103" s="49" t="n">
         <v>46322</v>
       </c>
-      <c r="Y103">
+      <c r="Y103" s="27">
         <f>CHOOSE(WEEKDAY(X103,2),"lunes","martes","miércoles","jueves","viernes","sábado","domingo")</f>
         <v/>
       </c>
-      <c r="Z103">
+      <c r="Z103" s="27">
         <f>INT((X103-MIN($X$2:$X$103))/7)+1</f>
         <v/>
       </c>
-      <c r="AA103">
+      <c r="AA103" s="27">
         <f>IF(X103=MIN($X$2:$X$103),"Lanzamiento","Calendario semanal")</f>
         <v/>
       </c>
@@ -27106,7 +27106,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="15" customHeight="1" s="28">
       <c r="A13" s="30" t="inlineStr">
         <is>
